--- a/docs/testing/SkyCraft-Network-Tests.xlsx
+++ b/docs/testing/SkyCraft-Network-Tests.xlsx
@@ -213,8 +213,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Start" displayName="Start" ref="A1:C9" headerRowCount="1">
-  <autoFilter ref="A1:C9"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Start" displayName="Start" ref="A1:C10" headerRowCount="1">
+  <autoFilter ref="A1:C10"/>
   <tableColumns count="3">
     <tableColumn id="1" name="№"/>
     <tableColumn id="2" name="Ситуация"/>
@@ -703,7 +703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -728,248 +728,265 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="44" customHeight="1">
+    <row r="2" ht="59" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Существующий SkyCraft работает</t>
+          <t>Автоматические проверки</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Распаковать friend-kit вне игры → Установить обновление.cmd → Проверить сборку.cmd → одиночный HUD/движение.</t>
+          <t>Открыть SkyCraft-Хост.exe, SkyCraft-Клиент.exe или SkyCraft-Без-друга.exe из нового комплекта. Папки определяются автоматически. Полный порядок: docs/YS-AUTOTEST.md. Ниже остаются подробные ручные проверки HUD/блоков/разных условий.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="44" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Первый тест с другом</t>
+          <t>Существующий SkyCraft работает</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>В одной LAN — L01. В разных сетях — I01: WAN IP/проброс TCP или доступный IPv6. Адрес получить по вкладке Адрес хоста, не наугад.</t>
+          <t>Распаковать friend-kit вне игры → Установить обновление.cmd → Проверить сборку.cmd → одиночный HUD/движение.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="44" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Читать конкретный сценарий</t>
+          <t>Первый тест с другом</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>В Сценарии подробно включить фильтр столбца ID, оставить нужный ID. Там полный порядок с командами и нужным Run ID. Подготовка и Адрес хоста объясняют источники переменных.</t>
+          <t>В одной LAN — L01. В разных сетях — I01: WAN IP/проброс TCP или доступный IPv6. Адрес получить по вкладке Адрес хоста, не наугад.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="44" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Ввод команд</t>
+          <t>Читать конкретный сценарий</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>T в Skyrim открывает чат Minecraft; /... вводить там. Команды Get-/Test- вводить в Windows PowerShell. Все подписи ENDPOINT/IP заменить своим значением.</t>
+          <t>В Сценарии подробно включить фильтр столбца ID, оставить нужный ID. Там полный порядок с командами и нужным Run ID. Подготовка и Адрес хоста объясняют источники переменных.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="44" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Ввод команд</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>T в Skyrim открывает чат Minecraft; /... вводить там. Команды Get-/Test- вводить в Windows PowerShell. Все подписи ENDPOINT/IP заменить своим значением.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="44" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Логи и результат</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Прогоны — наблюдения/метрики, Условия прогонов — адрес/версии/режимы. В конце два ZIP с одним ID. PASS TCP не означает PASS игрового сценария.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="42" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="8" ht="42" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Запуск без сети</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Проблема HUD/движения: Собрать отчёт.cmd режим 1. Он соберёт AUTO JSONL; ручной Run ID ещё не нужен.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="44" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Где файл настроек</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Сначала вкладка «Файлы и команды», G1–G5. Параметры join/network.* находятся в MINECRAFT\config\skycraft.properties. Пустой join = строка join= без текста после знака =.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Где файл настроек</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Сначала вкладка «Файлы и команды», G1–G5. Параметры join/network.* находятся в MINECRAFT\config\skycraft.properties. Пустой join = строка join= без текста после знака =.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="44" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Друг сейчас недоступен</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Вкладка «Без друга»: B0–B10 по порядку. Готовые команды, адреса loopback, пять отчётов и возврат DIRECT. Отдельная HTML: БЕЗ-ДРУГА.html.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Открыть: Файлы и команды</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Открыть: Подготовка</t>
+          <t>Открыть: Файлы и команды</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Открыть: Адрес хоста</t>
+          <t>Открыть: Подготовка</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Открыть: Настройка сети</t>
+          <t>Открыть: Адрес хоста</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Открыть: Без друга</t>
+          <t>Открыть: Настройка сети</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Открыть: Шаги</t>
+          <t>Открыть: Без друга</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Открыть: Матрица</t>
+          <t>Открыть: Шаги</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Открыть: Сценарии подробно</t>
+          <t>Открыть: Матрица</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Открыть: Прогоны</t>
+          <t>Открыть: Сценарии подробно</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Открыть: Условия прогонов</t>
+          <t>Открыть: Прогоны</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Открыть: Откуда данные</t>
+          <t>Открыть: Условия прогонов</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Открыть: Сбор отчёта</t>
+          <t>Открыть: Откуда данные</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="3" t="inlineStr">
         <is>
+          <t>Открыть: Сбор отчёта</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="3" t="inlineStr">
+        <is>
           <t>Открыть: Разбор сбоя</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
@@ -5164,7 +5181,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Проверьте активный JAR по установочному отчёту, один skycraft, версия network.2; английская раскладка и чат T.</t>
+          <t>Проверьте активный JAR по установочному отчёту, один skycraft, версия network.3; английская раскладка и чат T.</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -5651,12 +5668,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Каждый участник: закройте обе игры по G2. Если network.2 уже установлен, этот шаг пропустите. Если исходный SkyCraft 0.1.2 работает, запустите «Установить обновление.cmd» из P1; в ответ на запрос вставьте полный путь папки Minecraft из G1. Дождитесь сообщения об успешной установке. Если исходного SkyCraft ещё нет, сначала выполните docs/YS-FRIEND.md из комплекта.</t>
+          <t>Каждый участник: закройте обе игры по G2. Если network.3 уже установлен, этот шаг пропустите. Если исходный SkyCraft 0.1.2 работает, запустите «Установить обновление.cmd» из P1; в ответ на запрос вставьте полный путь папки Minecraft из G1. Дождитесь сообщения об успешной установке. Если исходного SkyCraft ещё нет, сначала выполните docs/YS-FRIEND.md из комплекта.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Старые SkyCraft/e4mc сохранятся в SkyCraft-YS-backups рядом с экземпляром. Настройки и миры сохраняются. Единственный активный JAR SkyCraft имеет версию 0.1.2-ys.network.2; e4mc отсутствует, Fabric API остаётся. Проверка версии и SHA256 — P3.</t>
+          <t>Старые SkyCraft/e4mc сохранятся в SkyCraft-YS-backups рядом с экземпляром. Настройки и миры сохраняются. Единственный активный JAR SkyCraft имеет версию 0.1.2-ys.network.3; e4mc отсутствует, Fabric API остаётся. Проверка версии и SHA256 — P3.</t>
         </is>
       </c>
     </row>
@@ -6396,7 +6413,7 @@
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>1. Распакуйте новый комплект целиком вне Skyrim. Откройте эту инструкцию, таблицу и Блокнот для заметок.
-2. Если network.2 уже установлен, повторная установка не нужна. Запустите «Проверить сборку.cmd»: путь Minecraft из G1, папка с SkyrimSE.exe, затем папка Mods вашего MO2 по подсказкам. Откройте полученный ПРОВЕРКА.txt по пути из программы. FAIL сначала разберите, WARN прочитайте.
+2. Если network.3 уже установлен, повторная установка не нужна. Запустите «Проверить сборку.cmd»: путь Minecraft из G1, папка с SkyrimSE.exe, затем папка Mods вашего MO2 по подсказкам. Откройте полученный ПРОВЕРКА.txt по пути из программы. FAIL сначала разберите, WARN прочитайте.
 3. Выполните G1–G5, включая копии и пять базовых строк G4. Запишите состояние VPN/Cloudflare/zapret; для первого прогона выключите их через интерфейсы программ.
 4. Загрузите тестовое сохранение, проверьте HUD, WASD и камеру. В чате:
 /skycraft debug status</t>
@@ -8074,7 +8091,7 @@
       <c r="D2" s="2" t="inlineStr">
         <is>
           <t>1. Распакуйте новый комплект целиком вне Skyrim. Откройте эту инструкцию, таблицу и Блокнот для заметок.
-2. Если network.2 уже установлен, повторная установка не нужна. Запустите «Проверить сборку.cmd»: путь Minecraft из G1, папка с SkyrimSE.exe, затем папка Mods вашего MO2 по подсказкам. Откройте полученный ПРОВЕРКА.txt по пути из программы. FAIL сначала разберите, WARN прочитайте.
+2. Если network.3 уже установлен, повторная установка не нужна. Запустите «Проверить сборку.cmd»: путь Minecraft из G1, папка с SkyrimSE.exe, затем папка Mods вашего MO2 по подсказкам. Откройте полученный ПРОВЕРКА.txt по пути из программы. FAIL сначала разберите, WARN прочитайте.
 3. Выполните G1–G5, включая копии и пять базовых строк G4. Запишите состояние VPN/Cloudflare/zapret; для первого прогона выключите их через интерфейсы программ.
 4. Загрузите тестовое сохранение, проверьте HUD, WASD и камеру. В чате:
 /skycraft debug status</t>
@@ -8218,7 +8235,7 @@
       <c r="D6" s="2" t="inlineStr">
         <is>
           <t>1. Распакуйте новый комплект целиком вне Skyrim. Откройте эту инструкцию, таблицу и Блокнот для заметок.
-2. Если network.2 уже установлен, повторная установка не нужна. Запустите «Проверить сборку.cmd»: путь Minecraft из G1, папка с SkyrimSE.exe, затем папка Mods вашего MO2 по подсказкам. Откройте полученный ПРОВЕРКА.txt по пути из программы. FAIL сначала разберите, WARN прочитайте.
+2. Если network.3 уже установлен, повторная установка не нужна. Запустите «Проверить сборку.cmd»: путь Minecraft из G1, папка с SkyrimSE.exe, затем папка Mods вашего MO2 по подсказкам. Откройте полученный ПРОВЕРКА.txt по пути из программы. FAIL сначала разберите, WARN прочитайте.
 3. Выполните G1–G5, включая копии и пять базовых строк G4. Запишите состояние VPN/Cloudflare/zapret; для первого прогона выключите их через интерфейсы программ.
 4. Загрузите тестовое сохранение, проверьте HUD, WASD и камеру. В чате:
 /skycraft debug status</t>
@@ -8329,7 +8346,7 @@
       <c r="D9" s="2" t="inlineStr">
         <is>
           <t>1. Распакуйте новый комплект целиком вне Skyrim. Откройте эту инструкцию, таблицу и Блокнот для заметок.
-2. Если network.2 уже установлен, повторная установка не нужна. Запустите «Проверить сборку.cmd»: путь Minecraft из G1, папка с SkyrimSE.exe, затем папка Mods вашего MO2 по подсказкам. Откройте полученный ПРОВЕРКА.txt по пути из программы. FAIL сначала разберите, WARN прочитайте.
+2. Если network.3 уже установлен, повторная установка не нужна. Запустите «Проверить сборку.cmd»: путь Minecraft из G1, папка с SkyrimSE.exe, затем папка Mods вашего MO2 по подсказкам. Откройте полученный ПРОВЕРКА.txt по пути из программы. FAIL сначала разберите, WARN прочитайте.
 3. Выполните G1–G5, включая копии и пять базовых строк G4. Запишите состояние VPN/Cloudflare/zapret; для первого прогона выключите их через интерфейсы программ.
 4. Загрузите тестовое сохранение, проверьте HUD, WASD и камеру. В чате:
 /skycraft debug status</t>

--- a/docs/testing/SkyCraft-Network-Tests.xlsx
+++ b/docs/testing/SkyCraft-Network-Tests.xlsx
@@ -7,38 +7,40 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Повтор network4" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Начать" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Файлы и команды" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Подготовка" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Адрес хоста" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Настройка сети" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Без друга" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Шаги" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Матрица" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Сценарии подробно" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Прогоны" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Условия прогонов" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Откуда данные" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Сбор отчёта" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Разбор сбоя" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Повтор network5" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Повтор network4" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Начать" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Файлы и команды" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Подготовка" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Адрес хоста" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Настройка сети" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Без друга" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Шаги" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Матрица" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Сценарии подробно" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Прогоны" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Условия прогонов" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Откуда данные" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Сбор отчёта" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Разбор сбоя" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Повтор network4'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Начать'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Файлы и команды'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Подготовка'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Адрес хоста'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Настройка сети'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Без друга'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="7">'Шаги'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="8">'Матрица'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="9">'Сценарии подробно'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="10">'Прогоны'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="11">'Условия прогонов'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="12">'Откуда данные'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="13">'Сбор отчёта'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="14">'Разбор сбоя'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Повтор network5'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Повтор network4'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Начать'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Файлы и команды'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Подготовка'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Адрес хоста'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Настройка сети'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'Без друга'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'Шаги'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'Матрица'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="10">'Сценарии подробно'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="11">'Прогоны'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="12">'Условия прогонов'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="13">'Откуда данные'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="14">'Сбор отчёта'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="15">'Разбор сбоя'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -215,8 +217,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AutomaticRetest4" displayName="AutomaticRetest4" ref="A1:F13" headerRowCount="1">
-  <autoFilter ref="A1:F13"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AutomaticRetest5" displayName="AutomaticRetest5" ref="A1:F14" headerRowCount="1">
+  <autoFilter ref="A1:F14"/>
   <tableColumns count="6">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Условия / порядок"/>
@@ -230,7 +232,22 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Detailed" displayName="Detailed" ref="A1:F289" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Scenarios" displayName="Scenarios" ref="A1:F26" headerRowCount="1">
+  <autoFilter ref="A1:F26"/>
+  <tableColumns count="6">
+    <tableColumn id="1" name="ID"/>
+    <tableColumn id="2" name="Сценарий"/>
+    <tableColumn id="3" name="Транспорт"/>
+    <tableColumn id="4" name="Минуты"/>
+    <tableColumn id="5" name="Условия"/>
+    <tableColumn id="6" name="PASS"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="Detailed" displayName="Detailed" ref="A1:F289" headerRowCount="1">
   <autoFilter ref="A1:F289"/>
   <tableColumns count="6">
     <tableColumn id="1" name="ID"/>
@@ -244,8 +261,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="Runs" displayName="Runs" ref="A1:O76" headerRowCount="1">
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="Runs" displayName="Runs" ref="A1:O76" headerRowCount="1">
   <autoFilter ref="A1:O76"/>
   <tableColumns count="15">
     <tableColumn id="1" name="Сценарий"/>
@@ -268,8 +285,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="RunConditions" displayName="RunConditions" ref="A1:K76" headerRowCount="1">
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="RunConditions" displayName="RunConditions" ref="A1:K76" headerRowCount="1">
   <autoFilter ref="A1:K76"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Run ID"/>
@@ -288,8 +305,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="Sources" displayName="Sources" ref="A1:C11" headerRowCount="1">
+<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="Sources" displayName="Sources" ref="A1:C11" headerRowCount="1">
   <autoFilter ref="A1:C11"/>
   <tableColumns count="3">
     <tableColumn id="1" name="Поле"/>
@@ -300,8 +317,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="ReportFields" displayName="ReportFields" ref="A1:D7" headerRowCount="1">
+<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="ReportFields" displayName="ReportFields" ref="A1:D7" headerRowCount="1">
   <autoFilter ref="A1:D7"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Код"/>
@@ -313,8 +330,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="Failures" displayName="Failures" ref="A1:C10" headerRowCount="1">
+<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="Failures" displayName="Failures" ref="A1:C10" headerRowCount="1">
   <autoFilter ref="A1:C10"/>
   <tableColumns count="3">
     <tableColumn id="1" name="Симптом"/>
@@ -326,7 +343,22 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Start" displayName="Start" ref="A1:C10" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="AutomaticRetest4" displayName="AutomaticRetest4" ref="A1:F13" headerRowCount="1">
+  <autoFilter ref="A1:F13"/>
+  <tableColumns count="6">
+    <tableColumn id="1" name="ID"/>
+    <tableColumn id="2" name="Условия / порядок"/>
+    <tableColumn id="3" name="Что делает хост"/>
+    <tableColumn id="4" name="Что делает клиент / один ПК"/>
+    <tableColumn id="5" name="Что измеряет программа"/>
+    <tableColumn id="6" name="Что передать / критерий"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Start" displayName="Start" ref="A1:C10" headerRowCount="1">
   <autoFilter ref="A1:C10"/>
   <tableColumns count="3">
     <tableColumn id="1" name="№"/>
@@ -337,8 +369,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="FilesCommands" displayName="FilesCommands" ref="A1:D9" headerRowCount="1">
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="FilesCommands" displayName="FilesCommands" ref="A1:D9" headerRowCount="1">
   <autoFilter ref="A1:D9"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Код"/>
@@ -350,8 +382,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Preparation" displayName="Preparation" ref="A1:D8" headerRowCount="1">
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Preparation" displayName="Preparation" ref="A1:D8" headerRowCount="1">
   <autoFilter ref="A1:D8"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Код"/>
@@ -363,8 +395,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Addresses" displayName="Addresses" ref="A1:D14" headerRowCount="1">
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Addresses" displayName="Addresses" ref="A1:D14" headerRowCount="1">
   <autoFilter ref="A1:D14"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Код"/>
@@ -376,8 +408,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Transports" displayName="Transports" ref="A1:D7" headerRowCount="1">
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Transports" displayName="Transports" ref="A1:D7" headerRowCount="1">
   <autoFilter ref="A1:D7"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Код"/>
@@ -389,8 +421,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="SinglePC" displayName="SinglePC" ref="A1:D13" headerRowCount="1">
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="SinglePC" displayName="SinglePC" ref="A1:D13" headerRowCount="1">
   <autoFilter ref="A1:D13"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Код"/>
@@ -402,8 +434,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Steps" displayName="Steps" ref="A1:E14" headerRowCount="1">
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Steps" displayName="Steps" ref="A1:E14" headerRowCount="1">
   <autoFilter ref="A1:E14"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Шаг"/>
@@ -411,21 +443,6 @@
     <tableColumn id="3" name="Хост"/>
     <tableColumn id="4" name="Клиент"/>
     <tableColumn id="5" name="Что фиксировать"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</table>
-</file>
-
-<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Scenarios" displayName="Scenarios" ref="A1:F26" headerRowCount="1">
-  <autoFilter ref="A1:F26"/>
-  <tableColumns count="6">
-    <tableColumn id="1" name="ID"/>
-    <tableColumn id="2" name="Сценарий"/>
-    <tableColumn id="3" name="Транспорт"/>
-    <tableColumn id="4" name="Минуты"/>
-    <tableColumn id="5" name="Условия"/>
-    <tableColumn id="6" name="PASS"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
@@ -720,7 +737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -776,7 +793,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Распаковать весь network.4 вне Skyrim. В помощнике выбрать реальную папку Minecraft. Закрыть обе игры → «Обновить мод».</t>
+          <t>Распаковать весь network.5 вне Skyrim. В помощнике выбрать реальную папку Minecraft. Закрыть обе игры → «Обновить мод».</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -786,7 +803,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Один SkyCraft JAR network.4, хэши, резервная копия прежнего JAR.</t>
+          <t>Один SkyCraft JAR network.5, хэши, резервная копия прежнего JAR.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -830,318 +847,350 @@
     <row r="4" ht="59" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>R2-SOLO</t>
+          <t>G03-AUTH</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Один ПК, 1–3 минуты</t>
+          <t>Автономный профиль / Недействительная сессия</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Не требуется.</t>
+          <t>До запуска: закрыть и вновь запустить Skyrim/Minecraft. Хост: Общая виртуальная сеть + DIRECT + галочка «Хост: автономные профили (частная LAN/Radmin)».</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>SkyCraft-Без-друга.exe → роль Без друга → DIRECT → код пустой → подписать условия → Начать автотест. Не двигаться. При падении отметить Ошибка, остановить и собрать отчёт.</t>
+          <t>Режим OFFLINE придёт в новом SCY2; самому менять properties не нужно. Для домашней LAN выбрать Одна локальная сеть.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Три закрытых порта / отказа / восстановления. Причина отказа, позиция, 5 секунд наблюдения, повторная доступность собственного сервера.</t>
+          <t>HOST_AUTHENTICATION сверяет выбранный и фактический режим хоста; должен быть OFFLINE. Наличие лицензии не устанавливается этим тестом.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Внешний ZIP с одного ПК. Допуск неподвижной позиции 3 блока. Интернет и два игрока NOT_RUN.</t>
+          <t>Имена в OFFLINE не подтверждаются Microsoft. У старого открытого LAN может остаться ONLINE: перезапустить игры. Подробности — АВТОТЕСТЫ.html.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="59" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>R2-SOLO</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Один ПК, 1–3 минуты</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Не требуется.</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>SkyCraft-Без-друга.exe → роль Без друга → DIRECT → код пустой → подписать условия → Начать автотест. Не двигаться. При падении отметить Ошибка, остановить и собрать отчёт.</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Три закрытых порта / отказа / восстановления. Причина отказа, позиция, 5 секунд наблюдения, повторная доступность собственного сервера.</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Внешний ZIP с одного ПК. Допуск неподвижной позиции 3 блока. Интернет и два игрока NOT_RUN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="59" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
           <t>R2-01</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Radmin; прежний zapret ALT на хосте; Cloudflare/VPN off; клиент чистый</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>SkyCraft-Хост.exe → Хост / Общая виртуальная сеть / DIRECT → условия R2-01 HOST → Начать автотест → дождаться HOST_LOCAL_TCP → Копировать код хоста → передать весь новый SCY2.</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>SkyCraft-Клиент.exe → Клиент / Общая виртуальная сеть / DIRECT → вставить новый SCY2 → условия R2-01 CLIENT → Начать автотест. IP/чат вручную не нужны.</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Radmin IPv4 первым; TCP отдельно от входа; ID/версия сервера; 180 с клиента, 240 с хоста; выход/позиция/повторный вход.</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Оба внешних ZIP. При отказе клиента хост нажимает Остановить и собрать отчёт, не ждёт 20 минут.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="44" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>R2-02</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Контроль: Radmin включён; оба без zapret/Cloudflare/VPN</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Завершить прошлый тест. Выставить условия. Новый прогон хоста и новый SCY2.</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>При необходимости /leave, остановиться. Новый код, сеть виртуальная, DIRECT. Подписать R2-02.</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Сравнение с R2-01 при одном изменённом факторе.</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Оба ZIP. Выполнять после успешного R2-01 либо анализа его отказа.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="44" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>R2-03</t>
+          <t>R2-02</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Хост zapret ALT + Cloudflare трафик и DNS, ваш UDP-профиль; клиент чистый</t>
+          <t>Контроль: Radmin включён; оба без zapret/Cloudflare/VPN</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Подключить настроенный Cloudflare через его интерфейс, записать профиль. Radmin оставить. Новый прогон/код.</t>
+          <t>Завершить прошлый тест. Выставить условия. Новый прогон хоста и новый SCY2.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Виртуальная сеть / DIRECT / новый код; в условиях записать фактический чистый режим.</t>
+          <t>При необходимости /leave, остановиться. Новый код, сеть виртуальная, DIRECT. Подписать R2-02.</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>winws-фильтры, WARP status/settings, маршруты до/после, TCP и игровой цикл.</t>
+          <t>Сравнение с R2-01 при одном изменённом факторе.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Оба ZIP. Disconnected не считается подключённым Cloudflare.</t>
+          <t>Оба ZIP. Выполнять после успешного R2-01 либо анализа его отказа.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="44" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>R2-04</t>
+          <t>R2-03</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Сложная комбинация у клиента, чистый хост</t>
+          <t>Хост zapret ALT + Cloudflare трафик и DNS, ваш UDP-профиль; клиент чистый</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Поменять роли и запустить нового хоста первым. Передать новый код.</t>
+          <t>Подключить настроенный Cloudflare через его интерфейс, записать профиль. Radmin оставить. Новый прогон/код.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Сложная комбинация zapret + Cloudflare у клиента; DIRECT, виртуальная сеть, новый код.</t>
+          <t>Виртуальная сеть / DIRECT / новый код; в условиях записать фактический чистый режим.</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Отдельная проверка исходящего пути клиента.</t>
+          <t>winws-фильтры, WARP status/settings, маршруты до/после, TCP и игровой цикл.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Оба ZIP с R2-04 и режимами каждого ПК.</t>
+          <t>Оба ZIP. Disconnected не считается подключённым Cloudflare.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>R2-04</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Сложная комбинация у клиента, чистый хост</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Поменять роли и запустить нового хоста первым. Передать новый код.</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Сложная комбинация zapret + Cloudflare у клиента; DIRECT, виртуальная сеть, новый код.</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Отдельная проверка исходящего пути клиента.</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Оба ZIP с R2-04 и режимами каждого ПК.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="44" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
           <t>R2-05</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>На обоих zapret + Cloudflare + VPN-туннель; Radmin</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Выставить свою комбинацию. Вписать название/режим VPN. Новый прогон/код.</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>То же; DIRECT следует маршрутам Windows, не отключает VPN.</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Выбранный Windows маршрут к IP хоста, WARP, слушающие порты; игровой цикл.</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Оба ZIP. Изменять условия внутри наблюдения не следует.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="59" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11" ht="59" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>R2-06</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>VPN клиента в режиме системного прокси</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Ранее успешные условия. Новый прогон/код.</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Найти настоящий SOCKS5/HTTP-порт в своём VPN. Выбрать SOCKS5/HTTP_CONNECT, вписать 127.0.0.1:реальный_порт, виртуальная сеть, новый код. Не копировать примерный порт.</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Прокси проверяется до адресов хоста, затем протокол/целевой доступ. PROXY_UNAVAILABLE отличается от TARGET_TCP_UNAVAILABLE.</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Оба ZIP. Если реальный порт неизвестен, этот сценарий NOT_RUN; не угадывать 8080.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="44" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="12" ht="44" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>R2-07</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Интернет без Radmin, если есть входящий путь</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Заранее доступный входящий TCP 25565 или глобальный IPv6. Новый код. WARP/VPN egress не гарантирует доступ.</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Сеть Разные сети / выбранный обоснованный транспорт / новый код. LAN и Radmin в этой строке не проверяются.</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Только глобальные кандидаты, TCP/login отдельно, маршруты/причины.</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Оба ZIP. Без входящего пути BLOCKED; ретранслятора в network.4 нет.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="59" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>VISUAL</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Во время парного наблюдения</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>0–60 с HUD; 60–120 с движение; 120–180 с подтвердить появление/исчезновение блока. Отметить списки в помощнике.</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>То же. К концу 180 с остановиться: программа сама вернёт в свой мир и повторно подключит. Блока нет → Не проверено.</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>VISUAL_* сохраняются как оценки человека; TCP не подменяет их.</t>
-        </is>
-      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Работает / Ошибка / Не проверено на обоих. Не загружать другие сохранения во время автоматического восстановления.</t>
+          <t>Оба ZIP. Без входящего пути BLOCKED; ретранслятора в network.5 нет.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="59" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>VISUAL</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Во время парного наблюдения</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0–60 с HUD; 60–120 с движение; 120–180 с подтвердить появление/исчезновение блока. Отметить списки в помощнике.</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>То же. К концу 180 с остановиться: программа сама вернёт в свой мир и повторно подключит. Блока нет → Не проверено.</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>VISUAL_* сохраняются как оценки человека; TCP не подменяет их.</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Работает / Ошибка / Не проверено на обоих. Не загружать другие сохранения во время автоматического восстановления.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="59" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
           <t>END</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>После каждого прогона</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Дождаться Готово: ZIP → Открыть отчёты. При отказе клиента остановить хост с отчётом.</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>То же. При успешном тесте остаётся у хоста; позднее T → /leave → Enter.</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Сохранение отсчётов также при остановке/обрыве; exact trace текущего прогона.</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Передать оба внешних ZIP из %LOCALAPPDATA%/SkyCraft/TestAssistant/reports; не только вложенный collector.zip.</t>
         </is>
@@ -1170,6 +1219,849 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:F26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="68" customWidth="1" min="5" max="5"/>
+    <col width="75" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Сценарий</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Транспорт</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Минуты</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Условия</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="44" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Логгер и открытие хоста</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Обычный режим сети; состояние каждого инструмента записать.</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Хост открыл порт; TCP доступен; отчёт содержит host_open, probe_result и trace_closed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="44" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Закрытый порт</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Порт 25566 не слушает никакая программа.</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Понятный отказ TCP; игра отвечает на ввод. PASS означает ожидаемый отказ, не успешный вход.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="44" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Недоступный прокси</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>SOCKS5 / HTTP_CONNECT</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Порт прокси свободен; каждый режим имеет отдельный Run ID.</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Отказ от прокси записан; зависания игры нет; восстановленный DIRECT снова проходит S01.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="44" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Настоящий пакет входа через прокси</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>HTTP_CONNECT</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>JDK 25 и настроенная среда разработки; установленный Prism не используется.</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>network-smoke-result.txt = PASS; JSONL содержит channel_active, HTTP 200 и trace_closed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="59" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>L01</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Базовая совместная игра</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Сначала P1–P7 и G1–G8. Все изменения join/network.* выполняйте в файле MINECRAFT\config\skycraft.properties по G2–G5. Оба: VPN, WARP, zapret выключены; DIRECT. Один физический роутер, A1–A3.</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Оба видят движение и изменения блоков; 5 минут без неожиданного разрыва; /leave возвращает свой мир.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="74" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>L02</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Смена хоста</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Сначала P1–P7 и G1–G8. Все изменения join/network.* выполняйте в файле MINECRAFT\config\skycraft.properties по G2–G5. Сначала L01 PASS. Поменять роли и получить новый LAN IPv4 по A1 на новом хосте.</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Успех при обеих ролях, отдельные архивы каждого ПК.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="59" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>L03</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Переподключение и уход хоста</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Сначала P1–P7 и G1–G8. Все изменения join/network.* выполняйте в файле MINECRAFT\config\skycraft.properties по G2–G5. Сначала L01 PASS; роли/адрес/режимы прежние.</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Понятный разрыв, без вечного автоповтора; повторный ручной вход работает.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="74" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>I01</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Разные сети, прямой вход</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Сначала P1–P7 и G1–G8. Все изменения join/network.* выполняйте в файле MINECRAFT\config\skycraft.properties по G2–G5. Разные сети. Оба DIRECT без инструментов. Хост: A4–A7 либо смена ролей, если входящий адрес есть только у друга.</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Общий цикл проходит и сохраняются два отчёта.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="59" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>I02</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>IPv6</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Сначала P1–P7 и G1–G8. Все изменения join/network.* выполняйте в файле MINECRAFT\config\skycraft.properties по G2–G5. Оба имеют рабочий глобальный IPv6, DIRECT; выполнить A8–A9.</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Вход и 5 минут совместной игры проходят.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="74" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>N01</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>zapret на клиенте</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Сначала P1–P7 и G1–G8. Все изменения join/network.* выполняйте в файле MINECRAFT\config\skycraft.properties по G2–G5. Сначала I01/L01 PASS. Хост остаётся базовым. Клиент включает только zapret, network.mode=DIRECT.</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Сравнить с базовым прогоном; общий цикл, нет обрывов.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="74" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>N02</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Cloudflare, только DNS на клиенте</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Сначала P1–P7 и G1–G8. Все изменения join/network.* выполняйте в файле MINECRAFT\config\skycraft.properties по G2–G5. Сначала L01/I01 PASS. Только клиент: Cloudflare DNS-only, без перенаправления трафика; DIRECT по C1.</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Полный цикл по IP проходит. При наличии собственного DNS-имени повторный цикл по имени проходит; без имени DNS-часть BLOCKED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="74" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>N03</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Cloudflare трафик + DNS (UDP)</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Сначала P1–P7 и G1–G8. Все изменения join/network.* выполняйте в файле MINECRAFT\config\skycraft.properties по G2–G5. Сначала базовый PASS. Только клиент: Cloudflare трафик+DNS, выбранный DNS-протокол UDP; DIRECT.</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Установление соединения, блоки в обе стороны, 10 минут без разрывов.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="59" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>N04</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>VPN-туннель на клиенте</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Сначала P1–P7 и G1–G8. Все изменения join/network.* выполняйте в файле MINECRAFT\config\skycraft.properties по G2–G5. Сначала базовый PASS. Только клиент: один VPN-туннель; DIRECT по C2.</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Игра следует маршрутам VPN, общий цикл проходит.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="74" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>N05</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Явный SOCKS5 VPN-клиента</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>SOCKS5</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Сначала P1–P7 и G1–G8. Все изменения join/network.* выполняйте в файле MINECRAFT\config\skycraft.properties по G2–G5. Сначала базовый PASS. Только клиент: включён SOCKS listener VPN-клиента; C3–C4.</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Удалённый DNS через прокси; TCP и игровой вход проходят.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="74" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>N06</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Явный HTTP CONNECT VPN-клиента</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>HTTP_CONNECT</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Сначала P1–P7 и G1–G8. Все изменения join/network.* выполняйте в файле MINECRAFT\config\skycraft.properties по G2–G5. Сначала базовый PASS. Только клиент: HTTP/mixed listener VPN-клиента; C3+C5.</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>В JSONL HTTP 200; вход в мир и изменения блоков проходят.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="74" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>N07</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>zapret + Cloudflare</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Сначала P1–P7 и G1–G8. Все изменения join/network.* выполняйте в файле MINECRAFT\config\skycraft.properties по G2–G5. Сначала N01/N03. Только клиент: zapret, затем Cloudflare traffic+DNS UDP; DIRECT.</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Сравнить с N01 и N03; 10 минут без разрывов.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="74" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>N08</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>zapret + Cloudflare + VPN-туннель</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Сначала P1–P7 и G1–G8. Все изменения join/network.* выполняйте в файле MINECRAFT\config\skycraft.properties по G2–G5. Сначала отдельные N01/N03/N04. Только клиент: zapret → Cloudflare traffic+DNS UDP → VPN tunnel; DIRECT.</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Вход и стабильность 15 минут; причины сбоев сравнить с одиночными режимами.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="74" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>N09</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Все инструменты + явный прокси</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>SOCKS5 / HTTP_CONNECT</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Сначала P1–P7 и G1–G8. Все изменения join/network.* выполняйте в файле MINECRAFT\config\skycraft.properties по G2–G5. Сначала N05/N06 и N07. Только клиент: zapret + Cloudflare traffic/DNS UDP + VPN в режиме системного прокси.</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Каждый транспорт оценивается отдельно; 15 минут игры на каждом доступном режиме.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="74" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>H01</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Инструменты на хосте</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Сначала P1–P7 и G1–G8. Все изменения join/network.* выполняйте в файле MINECRAFT\config\skycraft.properties по G2–G5. Сначала базовый PASS. Клиент остаётся базовым DIRECT. Хост включает zapret + Cloudflare traffic/DNS UDP.</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Проверить публикацию порта, вход клиента и стабильность каждого варианта.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="104" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>H02</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Инструменты на обоих ПК</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>DIRECT / явный прокси</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Сначала P1–P7 и G1–G8. Все изменения join/network.* выполняйте в файле MINECRAFT\config\skycraft.properties по G2–G5. Сначала H01 и нужный N08 либо N09 PASS. На обоих ПК zapret + Cloudflare трафик/DNS UDP + выбранный VPN. Для первой попытки оба VPN в режиме туннеля, клиент DIRECT C1. На хосте конфигурация SkyCraft C1; его VPN проверяется как изменение входящего маршрута.</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>15 минут, изменения в обе стороны, успешный /leave и повторный вход.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="44" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>E01</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Неправильный пароль прокси</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>SOCKS5 / HTTP_CONNECT</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Каждый транспорт отдельно; реальные секреты в Notes не писать.</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Отказ авторизации без зависания; восстановление пароля возвращает работоспособность.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="44" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>E02</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Отмена подключения</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>SOCKS5 / HTTP_CONNECT</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Нужна попытка, которая остаётся в ожидании достаточно долго.</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Поздний ответ не заменяет текущий мир; повторный вход работает; записать время отмены.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="104" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>E03</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>DNS-имя и IP одной цели</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>DIRECT / SOCKS5 / HTTP_CONNECT</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Сначала P1–P7 и G1–G8. Все изменения join/network.* выполняйте в файле MINECRAFT\config\skycraft.properties по G2–G5. Сначала рабочий I01. Требуется собственное DNS-имя, уже созданное владельцем домена и направленное на публичный IP хоста. Создание домена/DDNS в комплект не входит. Если имени нет — E03=BLOCKED, другие тесты по IP продолжайте.</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Выделить локальный DNS сбой в DIRECT и DNS/маршрут прокси в других режимах.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="104" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>E04</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>UDP недоступен</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>DIRECT / явный прокси</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Сначала P1–P7 и G1–G8. Все изменения join/network.* выполняйте в файле MINECRAFT\config\skycraft.properties по G2–G5. Дополнительный тест разработчика/подконтрольной сети. Готовая программа, которая блокирует и проверяет UDP, в комплект не входит. По умолчанию E04=BLOCKED: «нет подтверждённой среды без UDP». Не меняйте общий firewall или DNS Windows ради этого теста.</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Проверить Minecraft TCP при этих условиях, отметить возможный отказ самого VPN/DNS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="89" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>E05</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Переключение сети во время игры</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>DIRECT / явный прокси</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Сначала P1–P7 и G1–G8. Все изменения join/network.* выполняйте в файле MINECRAFT\config\skycraft.properties по G2–G5. Сначала N04 либо N05/N06 PASS. Клиент заранее выбирает второй рабочий VPN-сервер/профиль в своей программе, записывает исходный и новый профиль без ключей. Хост и игровой адрес сохраняются.</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Смена маршрута может оборвать TCP; требуется понятный разрыв и работоспособность ручного входа после стабилизации.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId25"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;CSkyCraft YS | &amp;P / &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId26"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:F289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -11033,7 +11925,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13374,7 +14266,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14745,7 +15637,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14943,214 +15835,6 @@
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Архивы содержат IP/адаптеры/метки. Пароли/аккаунты/конфиги целиком по умолчанию не собираются. Полные логи предварительно просмотреть.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;CSkyCraft YS | &amp;P / &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="110" customWidth="1" min="3" max="3"/>
-    <col width="85" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="36" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Код</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Этап</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Каждое поле / действие</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Где результат</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="134" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Если не запускается игра, HUD или чат</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>1. До нового запуска откройте папку распакованного комплекта и двойным щелчком запустите «Собрать отчёт.cmd».
-2. На «Режим [1]» введите 1 и Enter.
-3. На «Каталог Minecraft» вставьте полный путь из G1. Enter без ввода допустим только если показанный путь точно тот же.
-4. В описании укажите этап: Bethesda/меню/загрузка/HUD/чат, точное сообщение и время.
-5. На «Добавить latest.log, SkyCraft.log и логи SKSE?» ответьте no для обычного отчёта или yes, если нужны полные логи. При yes просмотрите их до передачи.</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Сборщик напечатает полный путь к созданному ZIP. Это STARTUP-client-…zip в папке reports внутри комплекта. Здесь собирается последний AUTO-лог запуска, если он есть. Автоматической отправки нет.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="89" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Как закончить размеченный тест</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>В чате игры по одной команде:
-/skycraft debug mark RUN_END
-/skycraft debug stop
-Подождите 2 секунды. Затем Alt+Tab и «Собрать отчёт.cmd» из распакованного комплекта → режим 2. Если игра аварийно закрылась, сразу собирайте отчёт с прежним ID, не запускайте игру ещё раз до сбора.</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>RUN_END — буквальная метка, заменять её не надо. ID указывается при debug start и в мастере сборщика. Если игра упала, отсутствие события trace_closed допустимо как факт сбоя, но запись отмечается незавершённой.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="119" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>R3</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Первые поля сетевого мастера</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>«Каталог Minecraft (с папкой mods)»: путь из G1.
-«Тот же ID, что в debug start»: ровно введённый ID, например S01_01.
-«Роль этого ПК»: Host, если лог был запущен с host; Client, если с client.
-«Где соединяются игроки»: Loopback для одного ПК и 127.0.0.1; LAN для одной домашней сети; Internet для разных сетей.
-«IP или DNS-имя хоста без порта»: только адрес, например 127.0.0.1. Для IPv6 без [] и без порта.
-«Порт игрового хоста»: отдельное число, например 25565.</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Все значения вводятся отдельными ответами и подтверждаются Enter. В S03 поле цели — игровой адрес 127.0.0.1 и порт 25565; недоступный прокси 127.0.0.1:25566 описывают в Notes. Это разные адреса.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="119" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>R4</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Режимы и итог в мастере</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>«zapret во время прогона»: off/on/unknown.
-«Cloudflare»: off/dns/traffic_dns/unknown.
-«VPN»: off/tunnel/system_proxy/unknown. Указывайте состояние ЭТОГО ПК в момент теста.
-«Итог»: pass/fail/blocked/not_run/partial, строчными буквами, как в подсказке. Для ожидаемого отказа S02/S03 pass означает правильную обработку отказа.
-«Что произошло»: режим SkyCraft (DIRECT/SOCKS5/HTTP_CONNECT), сообщения, время, наблюдения. Пароли, токены и ссылки подписки не пишите.</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Enter оставляет значение в квадратных скобках; не принимайте unknown/partial молча, если знаете результат. В таблице те же статусы написаны заглавными PASS/FAIL/BLOCKED/PARTIAL/NOT_RUN. Режим network.mode запишите в «Условия прогонов → Транспорт клиента».</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="149" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>R5</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Где лежит отчёт и как его прочитать</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>1. Скопируйте полный путь ZIP из последней строки мастера. Либо откройте reports внутри распакованного комплекта, отсортируйте по времени изменения и найдите имя с нужным ID и ролью.
-2. Для чтения: ПКМ по ZIP → «Извлечь всё» в отдельную папку. Откройте summary.json через «Открыть с помощью → Блокнот». Для events.csv в Excel: Данные → Из текста/CSV → выбрать файл → кодировка UTF-8 → разделитель точка с запятой → Загрузить. Исходный JSONL лежит в подпапке traces.
-3. В summary.json ищите TraceFiles, Events, TraceStopped, DroppedTraceEvents. TraceFiles &gt; 0 и Events &gt; 0 означают, что найден лог; TraceStopped=true — присутствует завершение.
-4. В events.csv включите Данные → Фильтр и отфильтруйте столбец event: host_open, probe_result, world_join, return_to_own_world, trace_closed.</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Для успешного netcheck событие probe_result имеет result=tcp_ready; для ожидаемого отказа — failed. Пустое поле/null означает отсутствие измерения, а не ноль. Для исходных логов: MINECRAFT\logs\skycraft-network; точный файл показывает /skycraft debug status. Отправляйте исходный ZIP отчёта, не заново упакованную папку.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="134" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>R6</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Как заполнить таблицу</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Откройте SkyCraft-Network-Tests.xlsx из docs\testing комплекта и сохраните свою рабочую копию.
-«Прогоны»: найдите Run ID, заполните итог, TCP, длительность в минутах и имя ZIP. Движение/блоки обоим и leave/rejoin для одного ПК — NOT_RUN, поля входа/пинга оставьте пустыми. Для двух ПК нужны наблюдения обеих сторон.
-«Условия прогонов»: та же строка ID; начало UTC из первого события environment, адрес:порт, источник адреса, версии, состояния программ для каждой участвующей стороны. Для одного ПК в поле второй стороны напишите «второго ПК нет».</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>S01_01: роль Host, Loopback, 127.0.0.1, порт 25565. S02_01: Client, Loopback, 127.0.0.1, порт 25566. S03_01/S03_02: Client, Loopback, 127.0.0.1, порт 25565. Во всех случаях впишите фактические состояния программ; для базовой проверки это off/off/off.
-Если нужно больше трёх попыток: в Excel перейдите в последнюю ячейку последней строки таблицы «Прогоны» и нажмите Tab — добавится строка. Укажите сценарий, новый ID и NOT_RUN; результаты заполните после теста. Так же добавьте строку того же ID в «Условия прогонов».</t>
         </is>
       </c>
     </row>
@@ -15177,6 +15861,214 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="110" customWidth="1" min="3" max="3"/>
+    <col width="85" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Код</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Каждое поле / действие</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Где результат</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="134" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Если не запускается игра, HUD или чат</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>1. До нового запуска откройте папку распакованного комплекта и двойным щелчком запустите «Собрать отчёт.cmd».
+2. На «Режим [1]» введите 1 и Enter.
+3. На «Каталог Minecraft» вставьте полный путь из G1. Enter без ввода допустим только если показанный путь точно тот же.
+4. В описании укажите этап: Bethesda/меню/загрузка/HUD/чат, точное сообщение и время.
+5. На «Добавить latest.log, SkyCraft.log и логи SKSE?» ответьте no для обычного отчёта или yes, если нужны полные логи. При yes просмотрите их до передачи.</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Сборщик напечатает полный путь к созданному ZIP. Это STARTUP-client-…zip в папке reports внутри комплекта. Здесь собирается последний AUTO-лог запуска, если он есть. Автоматической отправки нет.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="89" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Как закончить размеченный тест</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>В чате игры по одной команде:
+/skycraft debug mark RUN_END
+/skycraft debug stop
+Подождите 2 секунды. Затем Alt+Tab и «Собрать отчёт.cmd» из распакованного комплекта → режим 2. Если игра аварийно закрылась, сразу собирайте отчёт с прежним ID, не запускайте игру ещё раз до сбора.</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>RUN_END — буквальная метка, заменять её не надо. ID указывается при debug start и в мастере сборщика. Если игра упала, отсутствие события trace_closed допустимо как факт сбоя, но запись отмечается незавершённой.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="119" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Первые поля сетевого мастера</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>«Каталог Minecraft (с папкой mods)»: путь из G1.
+«Тот же ID, что в debug start»: ровно введённый ID, например S01_01.
+«Роль этого ПК»: Host, если лог был запущен с host; Client, если с client.
+«Где соединяются игроки»: Loopback для одного ПК и 127.0.0.1; LAN для одной домашней сети; Internet для разных сетей.
+«IP или DNS-имя хоста без порта»: только адрес, например 127.0.0.1. Для IPv6 без [] и без порта.
+«Порт игрового хоста»: отдельное число, например 25565.</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Все значения вводятся отдельными ответами и подтверждаются Enter. В S03 поле цели — игровой адрес 127.0.0.1 и порт 25565; недоступный прокси 127.0.0.1:25566 описывают в Notes. Это разные адреса.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="119" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Режимы и итог в мастере</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>«zapret во время прогона»: off/on/unknown.
+«Cloudflare»: off/dns/traffic_dns/unknown.
+«VPN»: off/tunnel/system_proxy/unknown. Указывайте состояние ЭТОГО ПК в момент теста.
+«Итог»: pass/fail/blocked/not_run/partial, строчными буквами, как в подсказке. Для ожидаемого отказа S02/S03 pass означает правильную обработку отказа.
+«Что произошло»: режим SkyCraft (DIRECT/SOCKS5/HTTP_CONNECT), сообщения, время, наблюдения. Пароли, токены и ссылки подписки не пишите.</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Enter оставляет значение в квадратных скобках; не принимайте unknown/partial молча, если знаете результат. В таблице те же статусы написаны заглавными PASS/FAIL/BLOCKED/PARTIAL/NOT_RUN. Режим network.mode запишите в «Условия прогонов → Транспорт клиента».</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="149" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Где лежит отчёт и как его прочитать</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1. Скопируйте полный путь ZIP из последней строки мастера. Либо откройте reports внутри распакованного комплекта, отсортируйте по времени изменения и найдите имя с нужным ID и ролью.
+2. Для чтения: ПКМ по ZIP → «Извлечь всё» в отдельную папку. Откройте summary.json через «Открыть с помощью → Блокнот». Для events.csv в Excel: Данные → Из текста/CSV → выбрать файл → кодировка UTF-8 → разделитель точка с запятой → Загрузить. Исходный JSONL лежит в подпапке traces.
+3. В summary.json ищите TraceFiles, Events, TraceStopped, DroppedTraceEvents. TraceFiles &gt; 0 и Events &gt; 0 означают, что найден лог; TraceStopped=true — присутствует завершение.
+4. В events.csv включите Данные → Фильтр и отфильтруйте столбец event: host_open, probe_result, world_join, return_to_own_world, trace_closed.</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Для успешного netcheck событие probe_result имеет result=tcp_ready; для ожидаемого отказа — failed. Пустое поле/null означает отсутствие измерения, а не ноль. Для исходных логов: MINECRAFT\logs\skycraft-network; точный файл показывает /skycraft debug status. Отправляйте исходный ZIP отчёта, не заново упакованную папку.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="134" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Как заполнить таблицу</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Откройте SkyCraft-Network-Tests.xlsx из docs\testing комплекта и сохраните свою рабочую копию.
+«Прогоны»: найдите Run ID, заполните итог, TCP, длительность в минутах и имя ZIP. Движение/блоки обоим и leave/rejoin для одного ПК — NOT_RUN, поля входа/пинга оставьте пустыми. Для двух ПК нужны наблюдения обеих сторон.
+«Условия прогонов»: та же строка ID; начало UTC из первого события environment, адрес:порт, источник адреса, версии, состояния программ для каждой участвующей стороны. Для одного ПК в поле второй стороны напишите «второго ПК нет».</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>S01_01: роль Host, Loopback, 127.0.0.1, порт 25565. S02_01: Client, Loopback, 127.0.0.1, порт 25566. S03_01/S03_02: Client, Loopback, 127.0.0.1, порт 25565. Во всех случаях впишите фактические состояния программ; для базовой проверки это off/off/off.
+Если нужно больше трёх попыток: в Excel перейдите в последнюю ячейку последней строки таблицы «Прогоны» и нажмите Tab — добавится строка. Укажите сценарий, новый ID и NOT_RUN; результаты заполните после теста. Так же добавьте строку того же ID в «Условия прогонов».</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;CSkyCraft YS | &amp;P / &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -15373,6 +16265,456 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="65" customWidth="1" min="3" max="3"/>
+    <col width="65" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Условия / порядок</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Что делает хост</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Что делает клиент / один ПК</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Что измеряет программа</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Что передать / критерий</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="44" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>G01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Обновить оба ПК</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Распаковать весь network.4 вне Skyrim. В помощнике выбрать реальную папку Minecraft. Закрыть обе игры → «Обновить мод».</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>То же. Minecraft: Prism → экземпляр → Папка Minecraft. Skyrim: папка SkyrimSE.exe. Моды MO2: настройки MO2 → Пути → Моды.</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Один SkyCraft JAR network.4, хэши, резервная копия прежнего JAR.</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Не запускать EXE из ZIP. Старые отчёты сохранить. Подробности: АВТОТЕСТЫ.html, раздел Подготовка.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="44" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>G02</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Загрузить сохранение</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>MO2 → SKSE → отдельное сохранение после Хелгена. Дождаться HUD/движения, встать на устойчивой поверхности.</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>То же. Не сохранять поверх основного сохранения.</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Живая связь Skyrim и готовая позиция до начала теста.</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Главного меню недостаточно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="59" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>R2-SOLO</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Один ПК, 1–3 минуты</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Не требуется.</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>SkyCraft-Без-друга.exe → роль Без друга → DIRECT → код пустой → подписать условия → Начать автотест. Не двигаться. При падении отметить Ошибка, остановить и собрать отчёт.</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Три закрытых порта / отказа / восстановления. Причина отказа, позиция, 5 секунд наблюдения, повторная доступность собственного сервера.</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Внешний ZIP с одного ПК. Допуск неподвижной позиции 3 блока. Интернет и два игрока NOT_RUN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="59" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>R2-01</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Radmin; прежний zapret ALT на хосте; Cloudflare/VPN off; клиент чистый</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>SkyCraft-Хост.exe → Хост / Общая виртуальная сеть / DIRECT → условия R2-01 HOST → Начать автотест → дождаться HOST_LOCAL_TCP → Копировать код хоста → передать весь новый SCY2.</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>SkyCraft-Клиент.exe → Клиент / Общая виртуальная сеть / DIRECT → вставить новый SCY2 → условия R2-01 CLIENT → Начать автотест. IP/чат вручную не нужны.</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Radmin IPv4 первым; TCP отдельно от входа; ID/версия сервера; 180 с клиента, 240 с хоста; выход/позиция/повторный вход.</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Оба внешних ZIP. При отказе клиента хост нажимает Остановить и собрать отчёт, не ждёт 20 минут.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>R2-02</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Контроль: Radmin включён; оба без zapret/Cloudflare/VPN</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Завершить прошлый тест. Выставить условия. Новый прогон хоста и новый SCY2.</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>При необходимости /leave, остановиться. Новый код, сеть виртуальная, DIRECT. Подписать R2-02.</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Сравнение с R2-01 при одном изменённом факторе.</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Оба ZIP. Выполнять после успешного R2-01 либо анализа его отказа.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="44" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>R2-03</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Хост zapret ALT + Cloudflare трафик и DNS, ваш UDP-профиль; клиент чистый</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Подключить настроенный Cloudflare через его интерфейс, записать профиль. Radmin оставить. Новый прогон/код.</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Виртуальная сеть / DIRECT / новый код; в условиях записать фактический чистый режим.</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>winws-фильтры, WARP status/settings, маршруты до/после, TCP и игровой цикл.</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Оба ZIP. Disconnected не считается подключённым Cloudflare.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="44" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>R2-04</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Сложная комбинация у клиента, чистый хост</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Поменять роли и запустить нового хоста первым. Передать новый код.</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Сложная комбинация zapret + Cloudflare у клиента; DIRECT, виртуальная сеть, новый код.</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Отдельная проверка исходящего пути клиента.</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Оба ZIP с R2-04 и режимами каждого ПК.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="44" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>R2-05</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>На обоих zapret + Cloudflare + VPN-туннель; Radmin</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Выставить свою комбинацию. Вписать название/режим VPN. Новый прогон/код.</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>То же; DIRECT следует маршрутам Windows, не отключает VPN.</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Выбранный Windows маршрут к IP хоста, WARP, слушающие порты; игровой цикл.</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Оба ZIP. Изменять условия внутри наблюдения не следует.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="59" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>R2-06</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>VPN клиента в режиме системного прокси</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Ранее успешные условия. Новый прогон/код.</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Найти настоящий SOCKS5/HTTP-порт в своём VPN. Выбрать SOCKS5/HTTP_CONNECT, вписать 127.0.0.1:реальный_порт, виртуальная сеть, новый код. Не копировать примерный порт.</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Прокси проверяется до адресов хоста, затем протокол/целевой доступ. PROXY_UNAVAILABLE отличается от TARGET_TCP_UNAVAILABLE.</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Оба ZIP. Если реальный порт неизвестен, этот сценарий NOT_RUN; не угадывать 8080.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="44" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>R2-07</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Интернет без Radmin, если есть входящий путь</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Заранее доступный входящий TCP 25565 или глобальный IPv6. Новый код. WARP/VPN egress не гарантирует доступ.</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Сеть Разные сети / выбранный обоснованный транспорт / новый код. LAN и Radmin в этой строке не проверяются.</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Только глобальные кандидаты, TCP/login отдельно, маршруты/причины.</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Оба ZIP. Без входящего пути BLOCKED; ретранслятора в network.4 нет.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="59" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>VISUAL</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Во время парного наблюдения</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0–60 с HUD; 60–120 с движение; 120–180 с подтвердить появление/исчезновение блока. Отметить списки в помощнике.</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>То же. К концу 180 с остановиться: программа сама вернёт в свой мир и повторно подключит. Блока нет → Не проверено.</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>VISUAL_* сохраняются как оценки человека; TCP не подменяет их.</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Работает / Ошибка / Не проверено на обоих. Не загружать другие сохранения во время автоматического восстановления.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="59" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>После каждого прогона</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Дождаться Готово: ZIP → Открыть отчёты. При отказе клиента остановить хост с отчётом.</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>То же. При успешном тесте остаётся у хоста; позднее T → /leave → Enter.</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Сохранение отсчётов также при остановке/обрыве; exact trace текущего прогона.</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Передать оба внешних ZIP из %LOCALAPPDATA%/SkyCraft/TestAssistant/reports; не только вложенный collector.zip.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;CSkyCraft YS | &amp;P / &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15679,7 +17021,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15912,217 +17254,6 @@
       <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Копию мира восстанавливают только при необходимости и при закрытых обеих играх: сначала сохраните текущее MINECRAFT\saves\SkyCraft под новым именем в backup, затем скопируйте исходную копию обратно как MINECRAFT\saves\SkyCraft. Это возвращает изменения мира к состоянию копии; без нужды мир не заменяйте.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;CSkyCraft YS | &amp;P / &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="90" customWidth="1" min="3" max="3"/>
-    <col width="65" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="36" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Код</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Действие</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Что сделать</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Ожидание</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="74" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Распаковать комплект</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Каждый участник: ПКМ по ZIP комплекта → «Извлечь всё» → выберите папку вне Skyrim, например D:\SkyCraftTest. Затем откройте полученную папку. Все названные здесь CMD находятся в её корне; запускайте их двойным щелчком из Проводника. Не запускайте CMD прямо внутри ZIP.</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>В папке есть НАЧАТЬ.txt, tools, docs, JAR и package-manifest.json. При проверке одному читайте «Без друга» B0–B11. Подробное объяснение путей и ввода — G1–G8.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="89" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Обновить Java-мод</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Каждый участник: закройте обе игры по G2. Если network.3 уже установлен, этот шаг пропустите. Если исходный SkyCraft 0.1.2 работает, запустите «Установить обновление.cmd» из P1; в ответ на запрос вставьте полный путь папки Minecraft из G1. Дождитесь сообщения об успешной установке. Если исходного SkyCraft ещё нет, сначала выполните docs/YS-FRIEND.md из комплекта.</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Старые SkyCraft/e4mc сохранятся в SkyCraft-YS-backups рядом с экземпляром. Настройки и миры сохраняются. Единственный активный JAR SkyCraft имеет версию 0.1.2-ys.network.3; e4mc отсутствует, Fabric API остаётся. Проверка версии и SHA256 — P3.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="104" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Проверить версии</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Каждый участник: запустите «Проверить сборку.cmd» из P1. Каталог Minecraft — G1; каталог Skyrim — папка с SkyrimSE.exe; каталог модов — MO2 → Настройки → Пути → Моды (Mods). Дождитесь пути отчёта, откройте ПРОВЕРКА.txt в созданной папке reports.
-В Prism: ПКМ по экземпляру → Редактировать → Версии: Minecraft 26.3, Loader 0.19.5, Fabric API 0.161.0+26.3. Java 25 проверяется в настройках Java экземпляра. В MO2 слева галочками включите SkyCraft и Address Library.</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Проверенный Skyrim runtime 1.7.104.0, SKSE 2.3.1, соответствующая Address Library. installation.json/ПРОВЕРКА.txt показывают факты и хеши. Каждый FAIL сначала разберите по его тексту; WARN прочитайте и проверьте вручную. Наличие файлов не подтверждает галочки MO2 и успешный запуск.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="89" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Проверить одиночный запуск</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Каждый участник выполняет G5: SKSE через MO2 → меню → отдельное тестовое сохранение после Хелгена → HUD Minecraft, WASD, камера. До изменений мира выполните копирование G3. Для двух ПК выберите одну и ту же локацию Skyrim, например одну точку на дороге у Ривервуда; запишите название и ориентир, используйте одинаковые моды, изменяющие эту локацию.</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Оба отдельно видят HUD и управляют игроком. При отсутствии HUD/ввода — отчёт R1. Не перезаписывайте основное сохранение. Мир Minecraft находится в MINECRAFT\saves\SkyCraft независимо от выбранного сохранения Skyrim.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="74" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>P5</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Найти чат</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>На загруженном сохранении нажмите T в окне Skyrim: исходный SkyCraft передаёт чат Minecraft и текстовый ввод через свой мост. Наберите /skycraft debug status и Enter. Escape закрывает чат. Набирайте команды латиницей; переключите раскладку на английскую. Отдельное окно Minecraft не требуется.</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>В чате ответ SkyCraft, а не «Unknown command». Если T не открыл чат, запишите это как отдельный сбой ввода; не продолжайте команды вслепую.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="119" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Создать исходные условия</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>На каждом ПК: закройте обе игры по G2 → сохраните копии G3 → откройте MINECRAFT\config\skycraft.properties → примените пять строк G4, включая join= и network.mode=DIRECT → Ctrl+S → запустите снова по G5.
-В своих VPN/Cloudflare/zapret запишите состояние до теста, затем выключите подключение/обработку через интерфейс каждой программы на время базовой проверки. Если у программы нет понятного выключателя, оставьте её состояние как unknown и запишите это; не завершайте неизвестные службы.</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Теперь ясно, какой файл изменён, и значения сохранены. Если нельзя отключить один из инструментов, базовую проверку обозначьте PARTIAL с фактическими условиями. После успешного L01/I01 проверяйте инструменты по отдельным сценариям. Для одного ПК используйте B0–B11.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="104" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>P7</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Назначить роли и ID</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Для двух ПК договоритесь: host владеет миром Minecraft и выполняет /skycraft host; client подключается командой /join. LAN: L01_01, разные сети IPv4: I01_01. Для новой попытки замените _01 на _02 во всех командах и мастерах обоих ПК.
-Откройте docs\testing\SkyCraft-Network-Tests.xlsx из P1, сохраните рабочую копию. В «Сценарии подробно» фильтром ID выберите сценарий; в «Условия прогонов» найдите строку того же Run ID. Правила заполнения — R6.</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>ID без пробелов/кириллицы, до 64 символов: латинские буквы, цифры, _ и -. На обоих ПК один ID, роли разные. Для одного ПК готовые ID/роли даны в B1–B9.</t>
         </is>
       </c>
     </row>
@@ -16149,13 +17280,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="96" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="90" customWidth="1" min="3" max="3"/>
+    <col width="65" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -16166,314 +17297,174 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Ветка</t>
+          <t>Действие</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Точные действия</t>
+          <t>Что сделать</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Что получить / ограничения</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="59" customHeight="1">
+          <t>Ожидание</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="74" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>A0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Выбрать ветку</t>
+          <t>Распаковать комплект</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Если оба ПК подключены к одному домашнему роутеру обычным Ethernet/Wi-Fi — A1–A3 (LAN). Если в разных квартирах/сетях — A4–A7 (Интернет IPv4) либо A8–A9 (IPv6). Доступ к одному VPN-провайдеру не делает ПК общей LAN. 127.0.0.1 — только текущий ПК.</t>
+          <t>Каждый участник: ПКМ по ZIP комплекта → «Извлечь всё» → выберите папку вне Skyrim, например D:\SkyCraftTest. Затем откройте полученную папку. Все названные здесь CMD находятся в её корне; запускайте их двойным щелчком из Проводника. Не запускайте CMD прямо внутри ZIP.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Назначьте переменные на бумаге: HOST_LAN_IP, HOST_ROUTER, HOST_WAN_IP, HOST_PORT=25565, EXTERNAL_PORT=25565, ENDPOINT. Это подписи, не текст для вставки в команду.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="74" customHeight="1">
+          <t>В папке есть НАЧАТЬ.txt, tools, docs, JAR и package-manifest.json. При проверке одному читайте «Без друга» B0–B11. Подробное объяснение путей и ввода — G1–G8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="89" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Найти LAN IPv4 хоста</t>
+          <t>Обновить Java-мод</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>На хосте, не на клиенте: «Адреса хоста.cmd» либо PowerShell: Get-NetIPConfiguration. Найдите подключённый Ethernet/Wi-Fi, к которому относятся оба ПК. Запишите IPv4Address и IPv4DefaultGateway.NextHop. Не выбирайте loopback, 169.254.*, WARP/VPN/виртуальный адаптер вместо вашей физической LAN.</t>
+          <t>Каждый участник: закройте обе игры по G2. Если network.3 уже установлен, этот шаг пропустите. Если исходный SkyCraft 0.1.2 работает, запустите «Установить обновление.cmd» из P1; в ответ на запрос вставьте полный путь папки Minecraft из G1. Дождитесь сообщения об успешной установке. Если исходного SkyCraft ещё нет, сначала выполните docs/YS-FRIEND.md из комплекта.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>HOST_LAN_IP = IPv4Address физического адаптера. HOST_ROUTER = его IPv4DefaultGateway.NextHop. Например 192.168.1.20 и 192.168.1.1; это примеры, берите свои значения.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="59" customHeight="1">
+          <t>Старые SkyCraft/e4mc сохранятся в SkyCraft-YS-backups рядом с экземпляром. Настройки и миры сохраняются. Единственный активный JAR SkyCraft имеет версию 0.1.2-ys.network.3; e4mc отсутствует, Fabric API остаётся. Проверка версии и SHA256 — P3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="104" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Передать LAN адрес</t>
+          <t>Проверить версии</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>После /skycraft host 25565 хост передаёт другу HOST_LAN_IP:25565 текстом. Если IPv4 хоста реально 192.168.1.20, готовая строка 192.168.1.20:25565. Клиент использует адрес ХОСТА, не свой IPv4 и не шлюз роутера.</t>
+          <t>Каждый участник: запустите «Проверить сборку.cmd» из P1. Каталог Minecraft — G1; каталог Skyrim — папка с SkyrimSE.exe; каталог модов — MO2 → Настройки → Пути → Моды (Mods). Дождитесь пути отчёта, откройте ПРОВЕРКА.txt в созданной папке reports.
+В Prism: ПКМ по экземпляру → Редактировать → Версии: Minecraft 26.3, Loader 0.19.5, Fabric API 0.161.0+26.3. Java 25 проверяется в настройках Java экземпляра. В MO2 слева галочками включите SkyCraft и Address Library.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>ENDPOINT = HOST_LAN_IP:HOST_PORT. Для LAN проброс порта на роутере не нужен. Гостевой Wi-Fi с изоляцией клиентов может запретить соединение.</t>
+          <t>Проверенный Skyrim runtime 1.7.104.0, SKSE 2.3.1, соответствующая Address Library. installation.json/ПРОВЕРКА.txt показывают факты и хеши. Каждый FAIL сначала разберите по его тексту; WARN прочитайте и проверьте вручную. Наличие файлов не подтверждает галочки MO2 и успешный запуск.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="89" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>A3</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Проверить LAN порт</t>
+          <t>Проверить одиночный запуск</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>После открытия мира клиент в PowerShell: Test-NetConnection -ComputerName HOST_LAN_IP -Port 25565 -InformationLevel Detailed. Подставьте свой адрес без :порт в ComputerName. Например: Test-NetConnection -ComputerName 192.168.1.20 -Port 25565. Смотрите TcpTestSucceeded, RemoteAddress, InterfaceAlias. Затем проверьте тот же адрес через /skycraft netcheck ENDPOINT в чате игры.</t>
+          <t>Каждый участник выполняет G5: SKSE через MO2 → меню → отдельное тестовое сохранение после Хелгена → HUD Minecraft, WASD, камера. До изменений мира выполните копирование G3. Для двух ПК выберите одну и ту же локацию Skyrim, например одну точку на дороге у Ривервуда; запишите название и ориентир, используйте одинаковые моды, изменяющие эту локацию.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>True/успех netcheck = TCP открыт. False: проверить, что хост не вышел из мира, порт 25565 слушается, выбрана правильная LAN, нет гостевой изоляции и разрешён входящий TCP. PingSucceeded отдельно успех не доказывает.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="134" customHeight="1">
+          <t>Оба отдельно видят HUD и управляют игроком. При отсутствии HUD/ввода — отчёт R1. Не перезаписывайте основное сохранение. Мир Minecraft находится в MINECRAFT\saves\SkyCraft независимо от выбранного сохранения Skyrim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="74" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>A4</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Найти WAN IPv4 в другой сети</t>
+          <t>Найти чат</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Хост сначала выполняет A1.
-1. Откройте браузер. В адресную строку введите http:// и свой HOST_ROUTER: например http://192.168.1.1, если шлюз именно такой. Если страница не открылась — адрес/HTTPS берётся из руководства вашего роутера.
-2. Войдите паролем администратора роутера (это может отличаться от пароля Wi-Fi).
-3. Откройте Internet/WAN/Статус подключения к провайдеру. Перепишите поле IPv4 адрес WAN и время; это HOST_WAN_IP. Названия меню зависят от модели, ищите состояние внешнего подключения, а не LAN. Если доступа к роутеру нет — внешний IPv4 тест пока BLOCKED.</t>
+          <t>На загруженном сохранении нажмите T в окне Skyrim: исходный SkyCraft передаёт чат Minecraft и текстовый ввод через свой мост. Наберите /skycraft debug status и Enter. Escape закрывает чат. Набирайте команды латиницей; переключите раскладку на английскую. Отдельное окно Minecraft не требуется.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Не копируйте выходной IP включённого VPN с сайта «мой IP». WAN 10.*, 192.168.*, 172.16.*–172.31.* или 100.64.*–100.127.* означает ещё один NAT; дальше A5. Если WAN изменится, старое приглашение перестанет подходить. Пароль роутера в отчёт не включается.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="74" customHeight="1">
+          <t>В чате ответ SkyCraft, а не «Unknown command». Если T не открыл чат, запишите это как отдельный сбой ввода; не продолжайте команды вслепую.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="119" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Проверить NAT и выбрать хоста</t>
+          <t>Создать исходные условия</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Если WAN частный: выясните, чей вышестоящий роутер. Для двух собственных роутеров TCP-порт надо направить на каждом; при CGNAT провайдера нужен доступный публичный адрес от провайдера либо глобальный IPv6. Если публичный вход есть только у друга, поменяйте host/client. Если нет у обоих — I01=BLOCKED; сохраняйте факт, не ставьте FAIL моду.</t>
+          <t>На каждом ПК: закройте обе игры по G2 → сохраните копии G3 → откройте MINECRAFT\config\skycraft.properties → примените пять строк G4, включая join= и network.mode=DIRECT → Ctrl+S → запустите снова по G5.
+В своих VPN/Cloudflare/zapret запишите состояние до теста, затем выключите подключение/обработку через интерфейс каждой программы на время базовой проверки. Если у программы нет понятного выключателя, оставьте её состояние как unknown и запишите это; не завершайте неизвестные службы.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Собственного ретранслятора/автоматического NAT traversal в этой сборке ещё нет. Клиентский SOCKS/HTTP-прокси не открывает входящий порт хоста. Отсутствие публичного входа конфигом не исправляется.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="179" customHeight="1">
+          <t>Теперь ясно, какой файл изменён, и значения сохранены. Если нельзя отключить один из инструментов, базовую проверку обозначьте PARTIAL с фактическими условиями. После успешного L01/I01 проверяйте инструменты по отдельным сценариям. Для одного ПК используйте B0–B11.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="104" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Направить TCP-порт на ПК хоста</t>
+          <t>Назначить роли и ID</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>На своём роутере A4:
-1. Откройте DHCP/список устройств. Найдите ПК хоста по HOST_LAN_IP из A1. Для него включите резервирование адреса (Address reservation/статическая аренда). MAC при необходимости берётся из этого устройства либо PowerShell: Get-NetAdapter | Select-Object Name,MacAddress,Status — тот же Ethernet/Wi-Fi A1.
-2. В Port forwarding/Virtual server/Переадресация портов нажмите «Добавить»: имя SkyCraft; протокол TCP; внешний порт 25565; внутренний IP HOST_LAN_IP; внутренний порт 25565; правило включено. Сохраните/Примените.
-3. Выполните F1 на Windows хоста. G5 запускает игру; в чате /skycraft host 25565.
-4. Из WAN поля A4 и внешнего порта правила составьте ENDPOINT, передайте его клиенту текстом.</t>
+          <t>Для двух ПК договоритесь: host владеет миром Minecraft и выполняет /skycraft host; client подключается командой /join. LAN: L01_01, разные сети IPv4: I01_01. Для новой попытки замените _01 на _02 во всех командах и мастерах обоих ПК.
+Откройте docs\testing\SkyCraft-Network-Tests.xlsx из P1, сохраните рабочую копию. В «Сценарии подробно» фильтром ID выберите сценарий; в «Условия прогонов» найдите строку того же Run ID. Правила заполнения — R6.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Пример: WAN 203.0.113.10 и внешний порт 30000 дают строку 203.0.113.10:30000; этот IP документационный, замените своим WAN. При внутреннем 25565 команда хоста остаётся /skycraft host 25565. Для двух собственных роутеров также A10. Если меню непонятно, остановитесь и укажите модель/непройденный шаг; не создавайте правило наугад.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="89" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>A7</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Проверить Интернет с клиента</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Клиент из другой сети: Test-NetConnection -ComputerName HOST_WAN_IP -Port EXTERNAL_PORT -InformationLevel Detailed. Затем /skycraft netcheck ENDPOINT выбранным игровым транспортом. Проверка своего WAN адреса с ПК хоста зависит от NAT loopback и не заменяет проверку друга. При VPN на хосте входящая доступность и обратный маршрут могут измениться — H01/H02 проверяют это заново.</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>ENDPOINT = WAN IPv4 хоста + внешний порт. True/TCP успех — можно идти к /join. Если timeout: WAN/NAT, проброс, Windows firewall, правила роутера, VPN хоста и фильтрация.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="74" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>A8</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Найти глобальный IPv6</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>На хосте: Get-NetIPAddress -AddressFamily IPv6 | Select-Object InterfaceAlias,IPAddress,AddressState. Нужен Preferred глобальный адрес подключённого адаптера с реальным IPv6 от провайдера. Не передавайте ::1, fe80:: (link-local), fc*/fd* (локальные ULA), 2001:db8:: (пример документации). Если выбор непонятен, пришлите результат и не угадывайте.</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>IPv6 ENDPOINT = [IPv6_ХОСТА]:25565, со скобками. В PowerShell ComputerName адрес без скобок и без :порт. Нужен рабочий IPv6 на обоих ПК.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="74" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>A9</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Проверить IPv6 снаружи</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Откройте мир на хосте. Для IPv6 обычно не нужна трансляция IPv4-порта; в IPv6 firewall роутера и Windows хоста разрешите входящий TCP 25565 к выбранному IPv6. Клиент: Test-NetConnection -ComputerName IPv6_ХОСТА -Port 25565. Затем /skycraft netcheck [IPv6_ХОСТА]:25565 и /join [IPv6_ХОСТА]:25565. После смены адреса IPv6 получите его заново.</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Успех TCP с клиента подтверждает доступ к порту. IPv6 от VPN не считать доступным входящим адресом без этой проверки.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="134" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>A10</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Два собственных роутера</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Только если оба роутера ваши и доступны: ПК хоста подключён к внутреннему роутеру, его WAN подключён к внешнему роутеру.
-1. На внутреннем роутере A6 направляет TCP 25565 на HOST_LAN_IP.
-2. Перепишите WAN IPv4 внутреннего роутера со страницы A4. Например 192.168.0.2.
-3. На внешнем роутере закрепите этот адрес за внутренним роутером; создайте TCP правило: внешний 25565 → IP 192.168.0.2, внутренний порт 25565. IP примера замените действительным WAN внутреннего роутера.
-4. Клиент получает публичный WAN именно внешнего роутера:25565; проверяет его по A7.</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Если вышестоящий NAT принадлежит провайдеру, правило на чужом роутере создать нельзя: запросите у провайдера публичный входящий IPv4 либо проверяйте глобальный IPv6 A8–A9. Без доступного адреса I01=BLOCKED, причину внесите в таблицу.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="89" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>F1</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Правило Windows firewall</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>На хосте Win+R → wf.msc → Правила для входящих подключений → Создать правило → Для порта → TCP → Определённые локальные порты: 25565 → Разрешить подключение → профиль вашей текущей сети (обычно Частный; при текущем Общедоступном нужен именно он) → имя SkyCraft TCP 25565. Для профиля сети: Get-NetConnectionProfile. Если Java уже разрешена и TCP проходит, нового правила не требуется.</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Правило открывает именно входящий игровой порт. Профиль «только Частный» не сработает, если активная сеть Windows «Общедоступная». После теста ненужное созданное правило можно удалить по этому имени.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="74" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>F2</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Порт слушается на хосте</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>После /skycraft host 25565 на хосте: Get-NetTCPConnection -State Listen -LocalPort 25565 | Select-Object LocalAddress,LocalPort,OwningProcess. Если пусто — сервер не открылся/закрыт или команда не выполнилась. Если порт занят до запуска хоста, выберите другой свободный внутренний порт и исправьте весь ENDPOINT/проброс/правило вместе.</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>LISTEN на нужном порту и сообщение «Мир открыт» — локальный сервер готов; внешний вход всё равно проверяет клиент. 0.0.0.0/:: в LISTEN — адрес привязки, не адрес приглашения.</t>
+          <t>ID без пробелов/кириллицы, до 64 символов: латинские буквы, цифры, _ и -. На обоих ПК один ID, роли разные. Для одного ПК готовые ID/роли даны в B1–B9.</t>
         </is>
       </c>
     </row>
@@ -16500,13 +17491,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="90" customWidth="1" min="3" max="3"/>
-    <col width="68" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="96" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -16517,7 +17508,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Режим</t>
+          <t>Ветка</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -16527,157 +17518,304 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Что проверить</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="149" customHeight="1">
+          <t>Что получить / ограничения</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="59" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>A0</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Начальная конфигурация DIRECT</t>
+          <t>Выбрать ветку</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>На указанном в сценарии ПК: G2–G5. Файл MINECRAFT\config\skycraft.properties должен содержать по одной строке:
-join=
-network.mode=DIRECT
-network.hostPort=25565
-network.advertisedAddress=
-network.timeoutMillis=10000
-Пустые значения — сразу конец строки после =. Если ключ отсутствовал, добавьте его в конец. Сохраните Ctrl+S и заново запустите SKSE/MO2.</t>
+          <t>Если оба ПК подключены к одному домашнему роутеру обычным Ethernet/Wi-Fi — A1–A3 (LAN). Если в разных квартирах/сетях — A4–A7 (Интернет IPv4) либо A8–A9 (IPv6). Доступ к одному VPN-провайдеру не делает ПК общей LAN. 127.0.0.1 — только текущий ПК.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Для туннельного VPN режим SkyCraft тоже DIRECT: соединение использует маршруты Windows. Имена параметров и значение DIRECT вписываются в файл, а не вводятся в чат. В /join вручную указывается игровой адрес.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="89" customHeight="1">
+          <t>Назначьте переменные на бумаге: HOST_LAN_IP, HOST_ROUTER, HOST_WAN_IP, HOST_PORT=25565, EXTERNAL_PORT=25565, ENDPOINT. Это подписи, не текст для вставки в команду.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="74" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>VPN в режиме туннеля</t>
+          <t>Найти LAN IPv4 хоста</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Для N04/N08 на клиенте: выполните C1, откройте свой VPN-клиент, выберите профиль/сервер, включите режим VPN/TUN/туннель и подключение. Запишите название программы, её версию, название сервера без ключей, время и порядок запуска. Для LAN найдите настройку Allow LAN/доступ к локальной сети; укажите её фактическое значение. Хост в этих сценариях остаётся с выключенными инструментами.</t>
+          <t>На хосте, не на клиенте: «Адреса хоста.cmd» либо PowerShell: Get-NetIPConfiguration. Найдите подключённый Ethernet/Wi-Fi, к которому относятся оба ПК. Запишите IPv4Address и IPv4DefaultGateway.NextHop. Не выбирайте loopback, 169.254.*, WARP/VPN/виртуальный адаптер вместо вашей физической LAN.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Названия кнопок зависят от VPN-программы; режим берите из её интерфейса, а не по наличию процесса. Если не можете определить режим, запишите unknown и PARTIAL. При пропаже TCP сравните InterfaceAlias/SourceAddress в выводе Test-NetConnection с базовым прогоном.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="149" customHeight="1">
+          <t>HOST_LAN_IP = IPv4Address физического адаптера. HOST_ROUTER = его IPv4DefaultGateway.NextHop. Например 192.168.1.20 и 192.168.1.1; это примеры, берите свои значения.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="59" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Найти адрес и порт прокси клиента</t>
+          <t>Передать LAN адрес</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>На клиенте откройте настройки используемой VPN/прокси-программы. Найдите поле SOCKS port / HTTP port / Mixed port / Local proxy: перепишите отдельно тип, адрес и порт. Если там нет адреса, смотрите документированный адрес прослушивания этой программы; не подставляйте его наугад.
-Для системного HTTP-прокси: Win+I → Сеть и Интернет → Прокси → ручная настройка, прочитайте адрес/порт. Один URL автоматического PAC-скрипта не является адресом proxy listener.
-В PowerShell по G6 проверьте реальный порт, например для порта 7890:
-Get-NetTCPConnection -State Listen -LocalPort 7890</t>
+          <t>После /skycraft host 25565 хост передаёт другу HOST_LAN_IP:25565 текстом. Если IPv4 хоста реально 192.168.1.20, готовая строка 192.168.1.20:25565. Клиент использует адрес ХОСТА, не свой IPv4 и не шлюз роутера.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7890 — пример; замените его числом из своей программы. PROXY_ENDPOINT = прокси на клиентском ПК, ENDPOINT = игровой хост. Если показан только TUN без HTTP/SOCKS listener, N05/N06 отметьте BLOCKED: сначала нужен поддерживаемый локальный прокси. Номер порта системного прокси не доказывает поддержку SOCKS5.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="164" customHeight="1">
+          <t>ENDPOINT = HOST_LAN_IP:HOST_PORT. Для LAN проброс порта на роутере не нужен. Гостевой Wi-Fi с изоляцией клиентов может запретить соединение.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="89" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Записать SOCKS5 в файл</t>
+          <t>Проверить LAN порт</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Только клиент: закройте обе игры по G2; откройте MINECRAFT\config\skycraft.properties; по G4 задайте:
-join=
-network.mode=SOCKS5
-network.proxy=АДРЕС_ПРОКСИ:ПОРТ_ПРОКСИ
-Замените последнюю строку фактическими значениями C3. Например network.proxy=127.0.0.1:7890 допустима только если ваша программа действительно предоставляет SOCKS5 на 7890.
-Если прокси требует имя и пароль, задайте отдельные строки network.proxy.username=ВАШЕ_ИМЯ и network.proxy.password=ВАШ_ПАРОЛЬ; если не требует — обе строки оставьте с пустым значением. Ctrl+S, запуск G5.</t>
+          <t>После открытия мира клиент в PowerShell: Test-NetConnection -ComputerName HOST_LAN_IP -Port 25565 -InformationLevel Detailed. Подставьте свой адрес без :порт в ComputerName. Например: Test-NetConnection -ComputerName 192.168.1.20 -Port 25565. Смотрите TcpTestSucceeded, RemoteAddress, InterfaceAlias. Затем проверьте тот же адрес через /skycraft netcheck ENDPOINT в чате игры.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Проверьте в чате /skycraft netcheck ENDPOINT, заменив ENDPOINT игровым адресом по A2/A7/A9. /join тоже получает игровой адрес. Секреты остаются в локальном файле; не копируйте его в отчёт. Игровое DNS-имя разрешает прокси.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="119" customHeight="1">
+          <t>True/успех netcheck = TCP открыт. False: проверить, что хост не вышел из мира, порт 25565 слушается, выбрана правильная LAN, нет гостевой изоляции и разрешён входящий TCP. PingSucceeded отдельно успех не доказывает.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="134" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>A4</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Записать HTTP CONNECT в файл</t>
+          <t>Найти WAN IPv4 в другой сети</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Только клиент: выполните G2–G5 для MINECRAFT\config\skycraft.properties. Параметры:
-join=
-network.mode=HTTP_CONNECT
-network.proxy=АДРЕС_ПРОКСИ:HTTP_ПОРТ
-Подставьте реальные значения HTTP/mixed listener из C3. Имя/пароль задайте отдельными ключами как в C4, либо оставьте оба пустыми при отсутствии авторизации. Затем в чате выполните /skycraft netcheck ENDPOINT с игровым адресом.</t>
+          <t>Хост сначала выполняет A1.
+1. Откройте браузер. В адресную строку введите http:// и свой HOST_ROUTER: например http://192.168.1.1, если шлюз именно такой. Если страница не открылась — адрес/HTTPS берётся из руководства вашего роутера.
+2. Войдите паролем администратора роутера (это может отличаться от пароля Wi-Fi).
+3. Откройте Internet/WAN/Статус подключения к провайдеру. Перепишите поле IPv4 адрес WAN и время; это HOST_WAN_IP. Названия меню зависят от модели, ищите состояние внешнего подключения, а не LAN. Если доступа к роутеру нет — внешний IPv4 тест пока BLOCKED.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>В events.csv по R5 смотрите status_code на этапе HTTP: 200 — туннель принят; 403/405 — запрет/неподдерживаемый CONNECT; 407 — требуется/не принята авторизация. Если разрешён только 443, нужен разрешённый внешний игровой порт и соответствующий проброс A6; простая замена числа в /join не создаёт сервер.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="89" customHeight="1">
+          <t>Не копируйте выходной IP включённого VPN с сайта «мой IP». WAN 10.*, 192.168.*, 172.16.*–172.31.* или 100.64.*–100.127.* означает ещё один NAT; дальше A5. Если WAN изменится, старое приглашение перестанет подходить. Пароль роутера в отчёт не включается.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="74" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Зафиксировать Cloudflare и zapret</t>
+          <t>Проверить NAT и выбрать хоста</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>В «Условия прогонов» для нужного Run ID, в столбце режимов ЭТОГО ПК, запишите название/версию Cloudflare One Client, режим DNS-only либо трафик+DNS, отображаемый DNS-протокол и название/версию zapret с выбранным профилем/имёнем запускаемого BAT. Версию ищите в «О программе» клиента; профиль zapret — в выбранном BAT/настройках запуска. Запишите порядок включения и UTC по G7. Меняйте сторону, указанную в сценарии.</t>
+          <t>Если WAN частный: выясните, чей вышестоящий роутер. Для двух собственных роутеров TCP-порт надо направить на каждом; при CGNAT провайдера нужен доступный публичный адрес от провайдера либо глобальный IPv6. Если публичный вход есть только у друга, поменяйте host/client. Если нет у обоих — I01=BLOCKED; сохраняйте факт, не ставьте FAIL моду.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Если интерфейс не показывает UDP, отметьте «DNS-протокол не подтверждён»: PARTIAL для условия UDP. Не приписывайте UDP по наличию warp-svc. Для N02/N03 прочие инструменты выключены; для N07–N09 их включают последовательно. Хост с инструментами проверяют H01/H02.</t>
+          <t>Собственного ретранслятора/автоматического NAT traversal в этой сборке ещё нет. Клиентский SOCKS/HTTP-прокси не открывает входящий порт хоста. Отсутствие публичного входа конфигом не исправляется.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="179" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Направить TCP-порт на ПК хоста</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>На своём роутере A4:
+1. Откройте DHCP/список устройств. Найдите ПК хоста по HOST_LAN_IP из A1. Для него включите резервирование адреса (Address reservation/статическая аренда). MAC при необходимости берётся из этого устройства либо PowerShell: Get-NetAdapter | Select-Object Name,MacAddress,Status — тот же Ethernet/Wi-Fi A1.
+2. В Port forwarding/Virtual server/Переадресация портов нажмите «Добавить»: имя SkyCraft; протокол TCP; внешний порт 25565; внутренний IP HOST_LAN_IP; внутренний порт 25565; правило включено. Сохраните/Примените.
+3. Выполните F1 на Windows хоста. G5 запускает игру; в чате /skycraft host 25565.
+4. Из WAN поля A4 и внешнего порта правила составьте ENDPOINT, передайте его клиенту текстом.</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Пример: WAN 203.0.113.10 и внешний порт 30000 дают строку 203.0.113.10:30000; этот IP документационный, замените своим WAN. При внутреннем 25565 команда хоста остаётся /skycraft host 25565. Для двух собственных роутеров также A10. Если меню непонятно, остановитесь и укажите модель/непройденный шаг; не создавайте правило наугад.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="89" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>A7</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Проверить Интернет с клиента</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Клиент из другой сети: Test-NetConnection -ComputerName HOST_WAN_IP -Port EXTERNAL_PORT -InformationLevel Detailed. Затем /skycraft netcheck ENDPOINT выбранным игровым транспортом. Проверка своего WAN адреса с ПК хоста зависит от NAT loopback и не заменяет проверку друга. При VPN на хосте входящая доступность и обратный маршрут могут измениться — H01/H02 проверяют это заново.</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>ENDPOINT = WAN IPv4 хоста + внешний порт. True/TCP успех — можно идти к /join. Если timeout: WAN/NAT, проброс, Windows firewall, правила роутера, VPN хоста и фильтрация.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="74" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>A8</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Найти глобальный IPv6</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>На хосте: Get-NetIPAddress -AddressFamily IPv6 | Select-Object InterfaceAlias,IPAddress,AddressState. Нужен Preferred глобальный адрес подключённого адаптера с реальным IPv6 от провайдера. Не передавайте ::1, fe80:: (link-local), fc*/fd* (локальные ULA), 2001:db8:: (пример документации). Если выбор непонятен, пришлите результат и не угадывайте.</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>IPv6 ENDPOINT = [IPv6_ХОСТА]:25565, со скобками. В PowerShell ComputerName адрес без скобок и без :порт. Нужен рабочий IPv6 на обоих ПК.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="74" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>A9</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Проверить IPv6 снаружи</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Откройте мир на хосте. Для IPv6 обычно не нужна трансляция IPv4-порта; в IPv6 firewall роутера и Windows хоста разрешите входящий TCP 25565 к выбранному IPv6. Клиент: Test-NetConnection -ComputerName IPv6_ХОСТА -Port 25565. Затем /skycraft netcheck [IPv6_ХОСТА]:25565 и /join [IPv6_ХОСТА]:25565. После смены адреса IPv6 получите его заново.</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Успех TCP с клиента подтверждает доступ к порту. IPv6 от VPN не считать доступным входящим адресом без этой проверки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="134" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>A10</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Два собственных роутера</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Только если оба роутера ваши и доступны: ПК хоста подключён к внутреннему роутеру, его WAN подключён к внешнему роутеру.
+1. На внутреннем роутере A6 направляет TCP 25565 на HOST_LAN_IP.
+2. Перепишите WAN IPv4 внутреннего роутера со страницы A4. Например 192.168.0.2.
+3. На внешнем роутере закрепите этот адрес за внутренним роутером; создайте TCP правило: внешний 25565 → IP 192.168.0.2, внутренний порт 25565. IP примера замените действительным WAN внутреннего роутера.
+4. Клиент получает публичный WAN именно внешнего роутера:25565; проверяет его по A7.</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Если вышестоящий NAT принадлежит провайдеру, правило на чужом роутере создать нельзя: запросите у провайдера публичный входящий IPv4 либо проверяйте глобальный IPv6 A8–A9. Без доступного адреса I01=BLOCKED, причину внесите в таблицу.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="89" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Правило Windows firewall</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>На хосте Win+R → wf.msc → Правила для входящих подключений → Создать правило → Для порта → TCP → Определённые локальные порты: 25565 → Разрешить подключение → профиль вашей текущей сети (обычно Частный; при текущем Общедоступном нужен именно он) → имя SkyCraft TCP 25565. Для профиля сети: Get-NetConnectionProfile. Если Java уже разрешена и TCP проходит, нового правила не требуется.</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Правило открывает именно входящий игровой порт. Профиль «только Частный» не сработает, если активная сеть Windows «Общедоступная». После теста ненужное созданное правило можно удалить по этому имени.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="74" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Порт слушается на хосте</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>После /skycraft host 25565 на хосте: Get-NetTCPConnection -State Listen -LocalPort 25565 | Select-Object LocalAddress,LocalPort,OwningProcess. Если пусто — сервер не открылся/закрыт или команда не выполнилась. Если порт занят до запуска хоста, выберите другой свободный внутренний порт и исправьте весь ENDPOINT/проброс/правило вместе.</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>LISTEN на нужном порту и сообщение «Мир открыт» — локальный сервер готов; внешний вход всё равно проверяет клиент. 0.0.0.0/:: в LISTEN — адрес привязки, не адрес приглашения.</t>
         </is>
       </c>
     </row>
@@ -16704,13 +17842,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="110" customWidth="1" min="3" max="3"/>
-    <col width="85" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="90" customWidth="1" min="3" max="3"/>
+    <col width="68" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -16721,337 +17859,167 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Тест</t>
+          <t>Режим</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Действия на одном ПК</t>
+          <t>Точные действия</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Ожидание и отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="134" customHeight="1">
+          <t>Что проверить</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="149" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>B0</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Подготовка без друга</t>
+          <t>Начальная конфигурация DIRECT</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>1. Распакуйте новый комплект целиком вне Skyrim. Откройте эту инструкцию, таблицу и Блокнот для заметок.
-2. Если network.3 уже установлен, повторная установка не нужна. Запустите «Проверить сборку.cmd»: путь Minecraft из G1, папка с SkyrimSE.exe, затем папка Mods вашего MO2 по подсказкам. Откройте полученный ПРОВЕРКА.txt по пути из программы. FAIL сначала разберите, WARN прочитайте.
-3. Выполните G1–G5, включая копии и пять базовых строк G4. Запишите состояние VPN/Cloudflare/zapret; для первого прогона выключите их через интерфейсы программ.
-4. Загрузите тестовое сохранение, проверьте HUD, WASD и камеру. В чате:
-/skycraft debug status</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Всё делаете вы на одном ПК. Второй Skyrim, второй Minecraft, внешний IP, вход в роутер и проброс порта для B1–B10 не нужны. PASS этих тестов означает только их собственное ожидание; совместную игру в таблице оставьте NOT_RUN.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="149" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>B1</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>S01_01: начать запись и открыть порт</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>После свежего запуска G5 откройте Windows PowerShell по G6:
-Get-NetTCPConnection -State Listen -LocalPort 25565 -ErrorAction SilentlyContinue
-Если вывод пустой — порт свободен. Если строка есть — остановитесь, не закрывайте неизвестный процесс; для этих готовых команд сначала освободите порт завершением известного старого SkyCraft либо пришлите вывод. Вернитесь в Skyrim. В чате по одной команде:
-/skycraft debug start S01_01 host
-/skycraft debug status
-/skycraft host 25565
-/skycraft debug mark HOST_READY</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>status показывает включённый логгер и путь с S01_01-host. Команда host отвечает «Мир открыт на порту 25565». Если «Мир уже открыт», для проверки host_open начните заново со свежего запуска G5 и нового ID S01_02. Ошибка порта/логгера — запишите её и соберите отчёт R2–R5.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="104" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>B2</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>S01_01: проверить TCP на своём ПК</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>В чате Skyrim:
-/skycraft netcheck 127.0.0.1:25565
-Дождитесь сообщения о доступном TCP. В Windows PowerShell:
-Get-NetTCPConnection -State Listen -LocalPort 25565 | Select-Object LocalAddress,LocalPort,OwningProcess
-Test-NetConnection -ComputerName 127.0.0.1 -Port 25565 -InformationLevel Detailed
-Скопируйте вывод в заметки. Вернитесь в игру, походите 2 минуты, убедитесь, что HUD и ввод работают.</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Ожидается строка порта LISTEN, TcpTestSucceeded=True и в чате «TCP … доступен». 127.0.0.1 здесь является готовым адресом текущего ПК. Не выполняйте /join 127.0.0.1:25565: вход в себя закроет собственный сервер и не создаст второго игрока.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="74" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>B3</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>S01_01: закончить и собрать отчёт</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Выполните R2. В мастере режима 2 по R3–R4 введите: ID S01_01; роль Host; сеть Loopback; адрес 127.0.0.1; порт 25565; фактические состояния программ; pass при выполнении B1–B2, иначе fail/partial с причиной. Notes: «S01; DIRECT; один ПК; LISTEN и TCP проверены; второго игрока нет».
-Проверьте отчёт по R5 и заполните R6.</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>В events.csv есть host_open, probe_result с tcp_ready и trace_closed. S01 может получить PASS; поля движения/блоков двух игроков и rejoin остаются NOT_RUN. Сохраните ZIP до следующего теста.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="179" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>B4</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>S02_01: проверить отказ на закрытом порту</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>1. Закройте обе игры по G2 и запустите их снова по G5 с базовыми строками G4. /host в этом тесте не выполняйте.
-2. В PowerShell:
-Get-NetTCPConnection -State Listen -LocalPort 25566 -ErrorAction SilentlyContinue
-Пустой вывод = никто не слушает. Если есть строка, остановите этот тест, не отключайте неизвестную программу.
-3. В чате Skyrim по одной команде:
-/skycraft debug start S02_01 client
-/skycraft netcheck 127.0.0.1:25566
-Дождитесь отказа. При timeoutMillis=10000 обычно ответ быстрее 15 секунд; если ответа нет, запишите время и не запускайте следующую проверку поверх незавершённой.</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Ожидаемый результат — отказ соединения, игра остаётся управляемой. Это намеренно неправильный адрес порта; появление ошибки здесь является успешной проверкой обработки ошибки.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="134" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>B5</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>S02_01: проверить восстановление своего мира</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>После ответа netcheck в том же чате:
-/join 127.0.0.1:25566
-Подождите возврата в свой Minecraft-мир. Запишите сообщение и длительность. Сеть должна отказать; загрузка своего мира занимает дополнительное время. Если спустя 60 секунд HUD/управление не восстановились, запишите это как FAIL восстановления и соберите отчёт. После восстановления:
-/skycraft debug mark OWN_WORLD_OK
-Проверьте WASD и чат в течение 2 минут с начала B4, затем R2. Мастер: S02_01, Client, Loopback, 127.0.0.1, 25566; pass только если отказ и восстановление выполнены.</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>В отчёте probe_result=failed; после /join ожидается return_to_own_world и затем world_join с result=local. Сохраните полный текст ошибки в Notes. Сеть в таблице: REFUSED или TIMEOUT по сообщению; сам сценарий может быть PASS.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="194" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>B6</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>S03_01: настроить намеренно отсутствующий SOCKS5</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>1. Сохраните отчёт S02. Закройте обе игры по G2.
-2. В PowerShell повторите проверку 25566 из B4: вывод должен быть пустым.
-3. Откройте MINECRAFT\config\skycraft.properties по G2. По G4 оставьте или добавьте строки:
+          <t>На указанном в сценарии ПК: G2–G5. Файл MINECRAFT\config\skycraft.properties должен содержать по одной строке:
 join=
-network.mode=SOCKS5
-network.proxy=127.0.0.1:25566
-network.proxy.username=
-network.proxy.password=
+network.mode=DIRECT
 network.hostPort=25565
 network.advertisedAddress=
 network.timeoutMillis=10000
-Сохраните и перезапустите по G5.</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Порт 25566 намеренно свободен; прокси на нём не запускаем. Пустые username/password нужны только этому отрицательному тесту. Реальные прежние значения находятся в копии G3.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="164" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>B7</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>S03_01: проверить SOCKS5 без скрытого DIRECT</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>В чате по одной команде:
-/skycraft debug start S03_01 client
-/skycraft host 25565
-В PowerShell проверьте прямую цель:
-Test-NetConnection -ComputerName 127.0.0.1 -Port 25565
-Должно быть TcpTestSucceeded=True. Вернитесь в чат:
-/skycraft netcheck 127.0.0.1:25565
-Ожидается отказ подключения через SOCKS5 к 127.0.0.1:25566. Проверьте ввод/HUD, запишите текст, затем R2. Мастер: S03_01, Client, Loopback, игровой адрес 127.0.0.1, игровой порт 25565; режим SOCKS5 и отсутствующий прокси 25566 — в Notes.</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Прямая игровая цель доступна, но выбранный прокси отсутствует. Успешный netcheck здесь — FAIL: он не должен обходить выбранный транспорт. Если не получилось открыть 25565, этот критерий не проверен: PARTIAL, сначала разберите порт. Наблюдайте не менее 3 минут с начала проверки.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="149" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>B8</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>S03_02: повторить для HTTP CONNECT</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>После сбора S03_01 закройте обе игры по G2. В MINECRAFT\config\skycraft.properties замените только строку режима на:
+Пустые значения — сразу конец строки после =. Если ключ отсутствовал, добавьте его в конец. Сохраните Ctrl+S и заново запустите SKSE/MO2.</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Для туннельного VPN режим SkyCraft тоже DIRECT: соединение использует маршруты Windows. Имена параметров и значение DIRECT вписываются в файл, а не вводятся в чат. В /join вручную указывается игровой адрес.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="89" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>VPN в режиме туннеля</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Для N04/N08 на клиенте: выполните C1, откройте свой VPN-клиент, выберите профиль/сервер, включите режим VPN/TUN/туннель и подключение. Запишите название программы, её версию, название сервера без ключей, время и порядок запуска. Для LAN найдите настройку Allow LAN/доступ к локальной сети; укажите её фактическое значение. Хост в этих сценариях остаётся с выключенными инструментами.</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Названия кнопок зависят от VPN-программы; режим берите из её интерфейса, а не по наличию процесса. Если не можете определить режим, запишите unknown и PARTIAL. При пропаже TCP сравните InterfaceAlias/SourceAddress в выводе Test-NetConnection с базовым прогоном.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="149" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Найти адрес и порт прокси клиента</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>На клиенте откройте настройки используемой VPN/прокси-программы. Найдите поле SOCKS port / HTTP port / Mixed port / Local proxy: перепишите отдельно тип, адрес и порт. Если там нет адреса, смотрите документированный адрес прослушивания этой программы; не подставляйте его наугад.
+Для системного HTTP-прокси: Win+I → Сеть и Интернет → Прокси → ручная настройка, прочитайте адрес/порт. Один URL автоматического PAC-скрипта не является адресом proxy listener.
+В PowerShell по G6 проверьте реальный порт, например для порта 7890:
+Get-NetTCPConnection -State Listen -LocalPort 7890</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7890 — пример; замените его числом из своей программы. PROXY_ENDPOINT = прокси на клиентском ПК, ENDPOINT = игровой хост. Если показан только TUN без HTTP/SOCKS listener, N05/N06 отметьте BLOCKED: сначала нужен поддерживаемый локальный прокси. Номер порта системного прокси не доказывает поддержку SOCKS5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="164" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Записать SOCKS5 в файл</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Только клиент: закройте обе игры по G2; откройте MINECRAFT\config\skycraft.properties; по G4 задайте:
+join=
+network.mode=SOCKS5
+network.proxy=АДРЕС_ПРОКСИ:ПОРТ_ПРОКСИ
+Замените последнюю строку фактическими значениями C3. Например network.proxy=127.0.0.1:7890 допустима только если ваша программа действительно предоставляет SOCKS5 на 7890.
+Если прокси требует имя и пароль, задайте отдельные строки network.proxy.username=ВАШЕ_ИМЯ и network.proxy.password=ВАШ_ПАРОЛЬ; если не требует — обе строки оставьте с пустым значением. Ctrl+S, запуск G5.</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Проверьте в чате /skycraft netcheck ENDPOINT, заменив ENDPOINT игровым адресом по A2/A7/A9. /join тоже получает игровой адрес. Секреты остаются в локальном файле; не копируйте его в отчёт. Игровое DNS-имя разрешает прокси.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="119" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Записать HTTP CONNECT в файл</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Только клиент: выполните G2–G5 для MINECRAFT\config\skycraft.properties. Параметры:
+join=
 network.mode=HTTP_CONNECT
-Остальные тестовые строки B6 оставьте. Сохраните по G4, запустите по G5. Повторите B7, используя команды:
-/skycraft debug start S03_02 client
-/skycraft host 25565
-/skycraft netcheck 127.0.0.1:25565
-Перед netcheck снова подтвердите прямой TCP PowerShell-командой B7. После 3 минут и R2 соберите отчёт: S03_02, Client, Loopback, 127.0.0.1, 25565; HTTP_CONNECT в Notes.</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Прямая цель доступна; отказ происходит на отсутствующем HTTP-прокси 25566. Два режима имеют два отдельных ZIP. Ожидаемый отказ — PASS, неожиданный обход — FAIL. /join в открытый на себе 25565 не выполняйте.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="104" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>B9</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Вернуть DIRECT и проверить восстановление</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>1. Закройте обе игры по G2. В файле MINECRAFT\config\skycraft.properties примените пять базовых строк G4; proxy/username/password можете вернуть из копии G3, при DIRECT они не используются. Сохраните и выполните G5.
-2. Повторите B1–B3 с новым ID S01_02 вместо S01_01 во всех командах и мастере.
-3. Убедитесь, что netcheck снова успешен и HUD работает.
-4. Верните исходные состояния сетевых программ. Если требуется полностью прежняя конфигурация — G8.</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Сохраните отдельный ZIP S01_02-host. Он подтверждает, что после отрицательных тестов базовый режим восстановился.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="89" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>B10</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Что передать после проверки одному</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Из reports распакованного комплекта: installation-*.zip проверки сборки; S01_01-host-*.zip; S02_01-client-*.zip; S03_01-client-*.zip; S03_02-client-*.zip; S01_02-host-*.zip. Имена могут включать UTC и дополнительные символы; выбирайте по ID и роли. Добавьте рабочую копию XLSX или текст с результатами каждого теста. Если HUD/чат не работали, вместо невыполненных тестов пришлите STARTUP-client-*.zip по R1 и напишите, где остановились.</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Эти тесты проверяют запуск, логгер, локальный TCP, обработку ошибок и восстановление. Внешняя доступность, NAT/CGNAT, вход другого игрока и совместное движение/блоки остаются NOT_RUN. Включение VPN для повторного loopback-теста проверит только этот локальный путь.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="89" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>B11</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Необязательный автоматический тест разработчика S04</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>В friend-kit исходников нет — там S04 оставьте NOT_RUN. На ПК с уже настроенными исходниками откройте PowerShell в папке source: в Проводнике откройте source, в адресной строке наберите powershell и Enter. Затем:
-powershell -NoProfile -ExecutionPolicy Bypass -File tools/dev.ps1 -Action NetworkSmoke
-Тест запускает отдельный Minecraft с локальным тестовым HTTP-прокси и закрывается сам. Пока он идёт, не запускайте новые ручные проверки.</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Результат: source\.tools\network-smoke-game\network-smoke-result.txt. Откройте в Блокноте, ожидается PASS. Этот тест проверяет настоящий пакет входа и HTTP CONNECT; второго игрового мира и другого игрока в нём нет.</t>
+network.proxy=АДРЕС_ПРОКСИ:HTTP_ПОРТ
+Подставьте реальные значения HTTP/mixed listener из C3. Имя/пароль задайте отдельными ключами как в C4, либо оставьте оба пустыми при отсутствии авторизации. Затем в чате выполните /skycraft netcheck ENDPOINT с игровым адресом.</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>В events.csv по R5 смотрите status_code на этапе HTTP: 200 — туннель принят; 403/405 — запрет/неподдерживаемый CONNECT; 407 — требуется/не принята авторизация. Если разрешён только 443, нужен разрешённый внешний игровой порт и соответствующий проброс A6; простая замена числа в /join не создаёт сервер.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="89" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Зафиксировать Cloudflare и zapret</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>В «Условия прогонов» для нужного Run ID, в столбце режимов ЭТОГО ПК, запишите название/версию Cloudflare One Client, режим DNS-only либо трафик+DNS, отображаемый DNS-протокол и название/версию zapret с выбранным профилем/имёнем запускаемого BAT. Версию ищите в «О программе» клиента; профиль zapret — в выбранном BAT/настройках запуска. Запишите порядок включения и UTC по G7. Меняйте сторону, указанную в сценарии.</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Если интерфейс не показывает UDP, отметьте «DNS-протокол не подтверждён»: PARTIAL для условия UDP. Не приписывайте UDP по наличию warp-svc. Для N02/N03 прочие инструменты выключены; для N07–N09 их включают последовательно. Хост с инструментами проверяют H01/H02.</t>
         </is>
       </c>
     </row>
@@ -17078,424 +18046,354 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="74" customWidth="1" min="4" max="4"/>
-    <col width="64" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="110" customWidth="1" min="3" max="3"/>
+    <col width="85" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Шаг</t>
+          <t>Код</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Этап</t>
+          <t>Тест</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Хост</t>
+          <t>Действия на одном ПК</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Клиент</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Что фиксировать</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="89" customHeight="1">
+          <t>Ожидание и отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="134" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>B0</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Зафиксировать условия</t>
+          <t>Подготовка без друга</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>В рабочей копии XLSX из P7 найдите строку RUN_ID в «Условия прогонов». По R6 запишите свои версии, режимы и внутренний порт 25565. Загрузите тестовое сохранение Skyrim в согласованной локации P4; SkyCraft автоматически открывает собственный мир MINECRAFT\saves\SkyCraft. До изменения блоков выполните G3.</t>
+          <t>1. Распакуйте новый комплект целиком вне Skyrim. Откройте эту инструкцию, таблицу и Блокнот для заметок.
+2. Если network.3 уже установлен, повторная установка не нужна. Запустите «Проверить сборку.cmd»: путь Minecraft из G1, папка с SkyrimSE.exe, затем папка Mods вашего MO2 по подсказкам. Откройте полученный ПРОВЕРКА.txt по пути из программы. FAIL сначала разберите, WARN прочитайте.
+3. Выполните G1–G5, включая копии и пять базовых строк G4. Запишите состояние VPN/Cloudflare/zapret; для первого прогона выключите их через интерфейсы программ.
+4. Загрузите тестовое сохранение, проверьте HUD, WASD и камеру. В чате:
+/skycraft debug status</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Заполните ту же строку XLSX своими версиями/режимами. Получите ENDPOINT по A2 для LAN, A6–A7 для внешнего IPv4 или A8–A9 для IPv6, запишите его и источник. Оставьте своё тестовое сохранение Skyrim загруженным. Настройки network.* перед прогоном изменяйте только в MINECRAFT\config\skycraft.properties по G2–G5.</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>RUN_ID замените названием выбранной попытки, например I01_01. Один Run ID у обоих ПК, роли host/client. Здесь ещё не нажимайте /join.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="89" customHeight="1">
+          <t>Всё делаете вы на одном ПК. Второй Skyrim, второй Minecraft, внешний IP, вход в роутер и проброс порта для B1–B10 не нужны. PASS этих тестов означает только их собственное ожидание; совместную игру в таблице оставьте NOT_RUN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="149" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Запустить лог</t>
+          <t>S01_01: начать запись и открыть порт</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>В чате Skyrim по G6, по одной команде:
-/skycraft debug start RUN_ID host
+          <t>После свежего запуска G5 откройте Windows PowerShell по G6:
+Get-NetTCPConnection -State Listen -LocalPort 25565 -ErrorAction SilentlyContinue
+Если вывод пустой — порт свободен. Если строка есть — остановитесь, не закрывайте неизвестный процесс; для этих готовых команд сначала освободите порт завершением известного старого SkyCraft либо пришлите вывод. Вернитесь в Skyrim. В чате по одной команде:
+/skycraft debug start S01_01 host
 /skycraft debug status
-RUN_ID замените ID попытки, например /skycraft debug start I01_01 host.</t>
+/skycraft host 25565
+/skycraft debug mark HOST_READY</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>В чате Skyrim, по одной команде:
-/skycraft debug start RUN_ID client
-/skycraft debug status
-Например /skycraft debug start I01_01 client.</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>status должен показать включённый логгер и путь JSONL с вашим ID и ролью. Запишите путь в заметки. Начало UTC после теста возьмите из первого события environment по G7/R5. При ошибке записи остановите прогон и соберите R1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="74" customHeight="1">
+          <t>status показывает включённый логгер и путь с S01_01-host. Команда host отвечает «Мир открыт на порту 25565». Если «Мир уже открыт», для проверки host_open начните заново со свежего запуска G5 и нового ID S01_02. Ошибка порта/логгера — запишите её и соберите отчёт R2–R5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="104" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Открыть мир</t>
+          <t>S01_01: проверить TCP на своём ПК</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>/skycraft host 25565. Дождитесь сообщения «Мир открыт на порту 25565», затем /skycraft debug mark HOST_READY. Проверьте LISTEN по F2. Если внешний порт отличается от 25565, внутри оставьте свой HOST_PORT; в приглашении передайте внешний.</t>
+          <t>В чате Skyrim:
+/skycraft netcheck 127.0.0.1:25565
+Дождитесь сообщения о доступном TCP. В Windows PowerShell:
+Get-NetTCPConnection -State Listen -LocalPort 25565 | Select-Object LocalAddress,LocalPort,OwningProcess
+Test-NetConnection -ComputerName 127.0.0.1 -Port 25565 -InformationLevel Detailed
+Скопируйте вывод в заметки. Вернитесь в игру, походите 2 минуты, убедитесь, что HUD и ввод работают.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Не выполняйте /host. Дождитесь от хоста сообщения готовности с ENDPOINT, например реальный IPv4:25565. Не закрывайте своё Skyrim-сохранение.</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Мир хоста открыт, порт слушается. Запишите внутренний и внешний порты в условиях. Хост не должен уходить из своего мира во время теста.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="89" customHeight="1">
+          <t>Ожидается строка порта LISTEN, TcpTestSucceeded=True и в чате «TCP … доступен». 127.0.0.1 здесь является готовым адресом текущего ПК. Не выполняйте /join 127.0.0.1:25565: вход в себя закроет собственный сервер и не создаст второго игрока.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="74" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>B3</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Проверить TCP и маршрут</t>
+          <t>S01_01: закончить и собрать отчёт</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Держите мир открытым; при False у клиента проверьте F1/F2 и A4–A7. Не выполняйте /join в свой мир из этого же экземпляра.</t>
+          <t>Выполните R2. В мастере режима 2 по R3–R4 введите: ID S01_01; роль Host; сеть Loopback; адрес 127.0.0.1; порт 25565; фактические состояния программ; pass при выполнении B1–B2, иначе fail/partial с причиной. Notes: «S01; DIRECT; один ПК; LISTEN и TCP проверены; второго игрока нет».
+Проверьте отчёт по R5 и заполните R6.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Для DIRECT выполните Windows-команду из A3/A7/A9 и запишите TcpTestSucceeded, RemoteAddress, InterfaceAlias. В чате: /skycraft netcheck ENDPOINT (замените целиком, например /skycraft netcheck 192.168.1.20:25565). При SOCKS/HTTP основной результат — netcheck, Windows TCP идёт напрямую.</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Успех TCP/netcheck не означает успешный игровой вход. При отказе зафиксируйте текст, UTC, режим, status_code/тип исключения; дальше шаги движения не выполняйте.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="74" customHeight="1">
+          <t>В events.csv есть host_open, probe_result с tcp_ready и trace_closed. S01 может получить PASS; поля движения/блоков двух игроков и rejoin остаются NOT_RUN. Сохраните ZIP до следующего теста.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="179" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>B4</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Войти в мир хоста</t>
+          <t>S02_01: проверить отказ на закрытом порту</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Оставаться в мире. Наблюдать появление второго игрока. Когда увидели его: /skycraft debug mark PEER_SEEN. Запишите, виден ли именно второй игрок, а не NPC Skyrim.</t>
+          <t>1. Закройте обе игры по G2 и запустите их снова по G5 с базовыми строками G4. /host в этом тесте не выполняйте.
+2. В PowerShell:
+Get-NetTCPConnection -State Listen -LocalPort 25566 -ErrorAction SilentlyContinue
+Пустой вывод = никто не слушает. Если есть строка, остановите этот тест, не отключайте неизвестную программу.
+3. В чате Skyrim по одной команде:
+/skycraft debug start S02_01 client
+/skycraft netcheck 127.0.0.1:25566
+Дождитесь отказа. При timeoutMillis=10000 обычно ответ быстрее 15 секунд; если ответа нет, запишите время и не запускайте следующую проверку поверх незавершённой.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>В чате /join ENDPOINT, например /join 192.168.1.20:25565 при этом реальном LAN адресе. Дождаться загрузки мира хоста, затем /skycraft debug mark JOIN_SEEN. /join закрывает ваш собственный Minecraft-мир на время гостевого входа; своё Skyrim-сохранение остаётся локальным.</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>У клиента в events.csv world_join с result=remote и elapsed_ms; у хоста два игрока. При ошибке — шаг X1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="104" customHeight="1">
+          <t>Ожидаемый результат — отказ соединения, игра остаётся управляемой. Это намеренно неправильный адрес порта; появление ошибки здесь является успешной проверкой обработки ошибки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="134" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>B5</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Проверить движение в обе стороны</t>
+          <t>S02_01: проверить восстановление своего мира</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Договоритесь текстом/голосом, кто идёт первым. Сначала хост WASD проходит от выбранного ориентира к другому примерно на 10 блоков и обратно; клиент наблюдает. Расстояние можно сверить по координатам XYZ экрана Minecraft F3: один блок = изменение X или Z на 1. Если F3 через мост не открывается, используйте оговорённые ориентиры и запишите это. Затем хост наблюдает тот же проход клиента.</t>
+          <t>После ответа netcheck в том же чате:
+/join 127.0.0.1:25566
+Подождите возврата в свой Minecraft-мир. Запишите сообщение и длительность. Сеть должна отказать; загрузка своего мира занимает дополнительное время. Если спустя 60 секунд HUD/управление не восстановились, запишите это как FAIL восстановления и соберите отчёт. После восстановления:
+/skycraft debug mark OWN_WORLD_OK
+Проверьте WASD и чат в течение 2 минут с начала B4, затем R2. Мастер: S02_01, Client, Loopback, 127.0.0.1, 25566; pass только если отказ и восстановление выполнены.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Сначала наблюдайте хоста, затем сами пройдите к тому же ориентиру и обратно. После подтверждения обоими в чате:
-/skycraft debug mark MOVE_BOTH_OK
-При откатах или невидимом игроке вместо этого:
-/skycraft debug mark MOVE_FAIL
-В заметках укажите, кто и что не видел, время UTC по G7.</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>В «Прогоны → Движение обоим» YES только если оба видели движение друг друга. Запишите дрожание, откаты и задержку. Пинг берётся из отчёта R5, не оценивается на глаз.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="119" customHeight="1">
+          <t>В отчёте probe_result=failed; после /join ожидается return_to_own_world и затем world_join с result=local. Сохраните полный текст ошибки в Notes. Сеть в таблице: REFUSED или TIMEOUT по сообщению; сам сценарий может быть PASS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="194" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>B6</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Проверить блоки в обе стороны</t>
+          <t>S03_01: настроить намеренно отсутствующий SOCKS5</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Выберите свободный тестовый участок. E открывает инвентарь Minecraft; выберите обычные доски/камень и перенесите в панель быстрого доступа, Escape закрывает инвентарь. Клавиши 1–9 выбирают слот. ПКМ по поверхности ставит блок, удержание ЛКМ по поставленному блоку ломает его. Хост ставит 3 отдельных блока, клиент подтверждает каждый, затем хост ломает их и клиент подтверждает исчезновение. После этого хост наблюдает действия клиента.</t>
+          <t>1. Сохраните отчёт S02. Закройте обе игры по G2.
+2. В PowerShell повторите проверку 25566 из B4: вывод должен быть пустым.
+3. Откройте MINECRAFT\config\skycraft.properties по G2. По G4 оставьте или добавьте строки:
+join=
+network.mode=SOCKS5
+network.proxy=127.0.0.1:25566
+network.proxy.username=
+network.proxy.password=
+network.hostPort=25565
+network.advertisedAddress=
+network.timeoutMillis=10000
+Сохраните и перезапустите по G5.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Подтвердите установку и удаление трёх блоков хоста, затем сами по тем же клавишам поставьте и сломайте три блока. После подтверждения обоими в чате:
-/skycraft debug mark BLOCK_BOTH_OK
-Если операция не дошла:
-/skycraft debug mark BLOCK_FAIL
-Запишите операцию, место и UTC.</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>«Блоки обоим» YES только после всех 12 операций: 3 установки + 3 удаления на каждой стороне. Не используйте TNT и разрушение поверхностей Skyrim. Если нет материалов или управление блоками не работает, запишите пропущенную проверку и PARTIAL; не считайте это доказательством сетевого сбоя.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="59" customHeight="1">
+          <t>Порт 25566 намеренно свободен; прокси на нём не запускаем. Пустые username/password нужны только этому отрицательному тесту. Реальные прежние значения находятся в копии G3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="164" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>B7</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Проверить стабильность</t>
+          <t>S03_01: проверить SOCKS5 без скрытого DIRECT</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Играть число минут из сценария, не выключать хост. Двигаться/строить безопасные блоки, следить за клиентом. Записать фактическое начало/конец и число неожиданных разрывов.</t>
+          <t>В чате по одной команде:
+/skycraft debug start S03_01 client
+/skycraft host 25565
+В PowerShell проверьте прямую цель:
+Test-NetConnection -ComputerName 127.0.0.1 -Port 25565
+Должно быть TcpTestSucceeded=True. Вернитесь в чат:
+/skycraft netcheck 127.0.0.1:25565
+Ожидается отказ подключения через SOCKS5 к 127.0.0.1:25566. Проверьте ввод/HUD, запишите текст, затем R2. Мастер: S03_01, Client, Loopback, игровой адрес 127.0.0.1, игровой порт 25565; режим SOCKS5 и отсутствующий прокси 25566 — в Notes.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Играть те же минуты. При каждом разрыве записать время и сообщение. Пинг берётся из клиентского summary.json PingMeanMs/PingMaxMs; клиентские sample.ping_ms пишутся раз в 5 секунд.</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Фактическая длительность не меньше требуемой. Любой разрыв записать, даже если повторный вход сработал. Краткий запуск — PARTIAL.</t>
+          <t>Прямая игровая цель доступна, но выбранный прокси отсутствует. Успешный netcheck здесь — FAIL: он не должен обходить выбранный транспорт. Если не получилось открыть 25565, этот критерий не проверен: PARTIAL, сначала разберите порт. Наблюдайте не менее 3 минут с начала проверки.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="149" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>B8</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Leave и повторный вход</t>
+          <t>S03_02: повторить для HTTP CONNECT</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Оставайтесь в мире. Поставьте один обычный блок в согласованном месте и оставьте его до повторного входа клиента. Клиент должен увидеть именно этот блок после возвращения.</t>
+          <t>После сбора S03_01 закройте обе игры по G2. В MINECRAFT\config\skycraft.properties замените только строку режима на:
+network.mode=HTTP_CONNECT
+Остальные тестовые строки B6 оставьте. Сохраните по G4, запустите по G5. Повторите B7, используя команды:
+/skycraft debug start S03_02 client
+/skycraft host 25565
+/skycraft netcheck 127.0.0.1:25565
+Перед netcheck снова подтвердите прямой TCP PowerShell-командой B7. После 3 минут и R2 соберите отчёт: S03_02, Client, Loopback, 127.0.0.1, 25565; HTTP_CONNECT в Notes.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>В чате, по одной команде:
-/skycraft debug mark LEAVE_BEGIN
-/leave
-Дождитесь своего мира и работающего HUD, затем:
-/skycraft debug mark OWN_WORLD_OK
-/join ENDPOINT
-В последней команде используйте тот же реальный игровой адрес, что в шаге 5. После входа подтвердите оставленный блок:
-/skycraft debug mark REJOIN_OK</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>«Leave / rejoin» OK только если свой мир восстановился, затем загрузился мир хоста и сохранился оставленный блок. При неудаче FAIL с текстом ошибки и UTC.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="89" customHeight="1">
+          <t>Прямая цель доступна; отказ происходит на отсутствующем HTTP-прокси 25566. Два режима имеют два отдельных ZIP. Ожидаемый отказ — PASS, неожиданный обход — FAIL. /join в открытый на себе 25565 не выполняйте.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="104" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>B9</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Остановить лог</t>
+          <t>Вернуть DIRECT и проверить восстановление</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>В чате:
-/skycraft debug mark RUN_END
-/skycraft debug stop
-Подождите 2 секунды. Держите хост открытым, пока клиент тоже не завершил запись и сбор отчёта.</t>
+          <t>1. Закройте обе игры по G2. В файле MINECRAFT\config\skycraft.properties примените пять базовых строк G4; proxy/username/password можете вернуть из копии G3, при DIRECT они не используются. Сохраните и выполните G5.
+2. Повторите B1–B3 с новым ID S01_02 вместо S01_01 во всех командах и мастере.
+3. Убедитесь, что netcheck снова успешен и HUD работает.
+4. Верните исходные состояния сетевых программ. Если требуется полностью прежняя конфигурация — G8.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>В чате:
-/skycraft debug mark RUN_END
-/skycraft debug stop
-Подождите 2 секунды. При аварийном закрытии игры сразу собирайте прежний ID без нового запуска.</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>R2 объясняет завершение. В summary.json поле TraceStopped=true соответствует событию trace_closed; DroppedTraceEvents показывает потерянные события логгера. Если завершения нет, запишите незавершённый лог.</t>
+          <t>Сохраните отдельный ZIP S01_02-host. Он подтверждает, что после отрицательных тестов базовый режим восстановился.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="89" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>B10</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Собрать ZIP</t>
+          <t>Что передать после проверки одному</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Запустите «Собрать отчёт.cmd» из распакованной папки P1. Режим 2. Заполните ВСЕ поля по R3–R4: путь G1, RUN_ID, Host, LAN/Internet, игровой адрес и отдельно порт, состояния своих программ и результат. Адрес тот же, которым пользовался клиент, включая внешний порт роутера.</t>
+          <t>Из reports распакованного комплекта: installation-*.zip проверки сборки; S01_01-host-*.zip; S02_01-client-*.zip; S03_01-client-*.zip; S03_02-client-*.zip; S01_02-host-*.zip. Имена могут включать UTC и дополнительные символы; выбирайте по ID и роли. Добавьте рабочую копию XLSX или текст с результатами каждого теста. Если HUD/чат не работали, вместо невыполненных тестов пришлите STARTUP-client-*.zip по R1 и напишите, где остановились.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Та же программа → 2. Поля по R3–R4: путь G1, RUN_ID, Client, та же сеть и игровой адрес/порт. При прокси в поле IP по-прежнему игровой хост; прокси/режим записываются в Notes. Для IPv6 адрес без [] и без порта.</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Сборщик выводит полный путь ZIP. Оба берут свои файлы из reports в корне комплекта по R5. Должны быть два ZIP с одинаковым ID и разными ролями.</t>
+          <t>Эти тесты проверяют запуск, логгер, локальный TCP, обработку ошибок и восстановление. Внешняя доступность, NAT/CGNAT, вход другого игрока и совместное движение/блоки остаются NOT_RUN. Включение VPN для повторного loopback-теста проверит только этот локальный путь.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="89" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>B11</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Заполнить итог</t>
+          <t>Необязательный автоматический тест разработчика S04</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Откройте рабочую XLSX, найдите строку RUN_ID в «Прогоны», заполните наблюдения и имя своего ZIP по R6. В «Условия прогонов» внесите адрес/источник и условия своего ПК. Согласуйте итог с клиентом.</t>
+          <t>В friend-kit исходников нет — там S04 оставьте NOT_RUN. На ПК с уже настроенными исходниками откройте PowerShell в папке source: в Проводнике откройте source, в адресной строке наберите powershell и Enter. Затем:
+powershell -NoProfile -ExecutionPolicy Bypass -File tools/dev.ps1 -Action NetworkSmoke
+Тест запускает отдельный Minecraft с локальным тестовым HTTP-прокси и закрывается сам. Пока он идёт, не запускайте новые ручные проверки.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Из своего распакованного отчёта R5 возьмите summary.json: RemoteJoinElapsedMs, PingMeanMs, PingMaxMs. RemoteJoinElapsedMs может быть списком попыток: выберите нужную по events.csv world_join с result=remote и запишите какую. Внесите имя своего ZIP. null/отсутствующее значение оставьте пустым.</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>PASS — выполнены все ожидания выбранного сценария; FAIL — ожидание нарушено; BLOCKED — нет условий; PARTIAL — часть шагов не проверена. Передайте два исходных ZIP и заполненную рабочую XLSX.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="104" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>X1</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Если вход не удался</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Проверьте F2, запишите вывод LISTEN и оставался ли хост в своём мире. В чате:
-/skycraft debug mark JOIN_FAIL_HOST
-/skycraft debug stop
-Пауза 2 секунды, отчёт режима 2 по R3–R5 с прежним ID и Host.</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Запишите полный видимый текст ошибки и UTC G7. После возврата в свой мир:
-/skycraft debug mark JOIN_FAIL
-/skycraft debug stop
-Пауза 2 секунды, отчёт режима 2 с прежним ID и Client. Если игра упала, собирайте сразу, не запускайте снова.</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>После отказа пропустите шаги 6–9. Для новой попытки новый номер ID. Сохраните оба отчёта даже при неуспехе.</t>
+          <t>Результат: source\.tools\network-smoke-game\network-smoke-result.txt. Откройте в Блокноте, ожидается PASS. Этот тест проверяет настоящий пакет входа и HTTP CONNECT; второго игрового мира и другого игрока в нём нет.</t>
         </is>
       </c>
     </row>
@@ -17522,827 +18420,428 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="68" customWidth="1" min="5" max="5"/>
-    <col width="75" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="74" customWidth="1" min="4" max="4"/>
+    <col width="64" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>Шаг</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Сценарий</t>
+          <t>Этап</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Транспорт</t>
+          <t>Хост</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Минуты</t>
+          <t>Клиент</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Условия</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="44" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>S01</t>
+          <t>Что фиксировать</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="89" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Логгер и открытие хоста</t>
+          <t>Зафиксировать условия</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>DIRECT</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>2</v>
+          <t>В рабочей копии XLSX из P7 найдите строку RUN_ID в «Условия прогонов». По R6 запишите свои версии, режимы и внутренний порт 25565. Загрузите тестовое сохранение Skyrim в согласованной локации P4; SkyCraft автоматически открывает собственный мир MINECRAFT\saves\SkyCraft. До изменения блоков выполните G3.</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Заполните ту же строку XLSX своими версиями/режимами. Получите ENDPOINT по A2 для LAN, A6–A7 для внешнего IPv4 или A8–A9 для IPv6, запишите его и источник. Оставьте своё тестовое сохранение Skyrim загруженным. Настройки network.* перед прогоном изменяйте только в MINECRAFT\config\skycraft.properties по G2–G5.</t>
+        </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Обычный режим сети; состояние каждого инструмента записать.</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Хост открыл порт; TCP доступен; отчёт содержит host_open, probe_result и trace_closed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="44" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>S02</t>
+          <t>RUN_ID замените названием выбранной попытки, например I01_01. Один Run ID у обоих ПК, роли host/client. Здесь ещё не нажимайте /join.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="89" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Закрытый порт</t>
+          <t>Запустить лог</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>DIRECT</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>2</v>
+          <t>В чате Skyrim по G6, по одной команде:
+/skycraft debug start RUN_ID host
+/skycraft debug status
+RUN_ID замените ID попытки, например /skycraft debug start I01_01 host.</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>В чате Skyrim, по одной команде:
+/skycraft debug start RUN_ID client
+/skycraft debug status
+Например /skycraft debug start I01_01 client.</t>
+        </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Порт 25566 не слушает никакая программа.</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Понятный отказ TCP; игра отвечает на ввод. PASS означает ожидаемый отказ, не успешный вход.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="44" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>S03</t>
+          <t>status должен показать включённый логгер и путь JSONL с вашим ID и ролью. Запишите путь в заметки. Начало UTC после теста возьмите из первого события environment по G7/R5. При ошибке записи остановите прогон и соберите R1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="74" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Недоступный прокси</t>
+          <t>Открыть мир</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>SOCKS5 / HTTP_CONNECT</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>3</v>
+          <t>/skycraft host 25565. Дождитесь сообщения «Мир открыт на порту 25565», затем /skycraft debug mark HOST_READY. Проверьте LISTEN по F2. Если внешний порт отличается от 25565, внутри оставьте свой HOST_PORT; в приглашении передайте внешний.</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Не выполняйте /host. Дождитесь от хоста сообщения готовности с ENDPOINT, например реальный IPv4:25565. Не закрывайте своё Skyrim-сохранение.</t>
+        </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Порт прокси свободен; каждый режим имеет отдельный Run ID.</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Отказ от прокси записан; зависания игры нет; восстановленный DIRECT снова проходит S01.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="44" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>S04</t>
+          <t>Мир хоста открыт, порт слушается. Запишите внутренний и внешний порты в условиях. Хост не должен уходить из своего мира во время теста.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="89" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Настоящий пакет входа через прокси</t>
+          <t>Проверить TCP и маршрут</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>HTTP_CONNECT</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>2</v>
+          <t>Держите мир открытым; при False у клиента проверьте F1/F2 и A4–A7. Не выполняйте /join в свой мир из этого же экземпляра.</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Для DIRECT выполните Windows-команду из A3/A7/A9 и запишите TcpTestSucceeded, RemoteAddress, InterfaceAlias. В чате: /skycraft netcheck ENDPOINT (замените целиком, например /skycraft netcheck 192.168.1.20:25565). При SOCKS/HTTP основной результат — netcheck, Windows TCP идёт напрямую.</t>
+        </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>JDK 25 и настроенная среда разработки; установленный Prism не используется.</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>network-smoke-result.txt = PASS; JSONL содержит channel_active, HTTP 200 и trace_closed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="59" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>L01</t>
+          <t>Успех TCP/netcheck не означает успешный игровой вход. При отказе зафиксируйте текст, UTC, режим, status_code/тип исключения; дальше шаги движения не выполняйте.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="74" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Базовая совместная игра</t>
+          <t>Войти в мир хоста</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>DIRECT</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>5</v>
+          <t>Оставаться в мире. Наблюдать появление второго игрока. Когда увидели его: /skycraft debug mark PEER_SEEN. Запишите, виден ли именно второй игрок, а не NPC Skyrim.</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>В чате /join ENDPOINT, например /join 192.168.1.20:25565 при этом реальном LAN адресе. Дождаться загрузки мира хоста, затем /skycraft debug mark JOIN_SEEN. /join закрывает ваш собственный Minecraft-мир на время гостевого входа; своё Skyrim-сохранение остаётся локальным.</t>
+        </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Сначала P1–P7 и G1–G8. Все изменения join/network.* выполняйте в файле MINECRAFT\config\skycraft.properties по G2–G5. Оба: VPN, WARP, zapret выключены; DIRECT. Один физический роутер, A1–A3.</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Оба видят движение и изменения блоков; 5 минут без неожиданного разрыва; /leave возвращает свой мир.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="74" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>L02</t>
+          <t>У клиента в events.csv world_join с result=remote и elapsed_ms; у хоста два игрока. При ошибке — шаг X1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="104" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Смена хоста</t>
+          <t>Проверить движение в обе стороны</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>DIRECT</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>5</v>
+          <t>Договоритесь текстом/голосом, кто идёт первым. Сначала хост WASD проходит от выбранного ориентира к другому примерно на 10 блоков и обратно; клиент наблюдает. Расстояние можно сверить по координатам XYZ экрана Minecraft F3: один блок = изменение X или Z на 1. Если F3 через мост не открывается, используйте оговорённые ориентиры и запишите это. Затем хост наблюдает тот же проход клиента.</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Сначала наблюдайте хоста, затем сами пройдите к тому же ориентиру и обратно. После подтверждения обоими в чате:
+/skycraft debug mark MOVE_BOTH_OK
+При откатах или невидимом игроке вместо этого:
+/skycraft debug mark MOVE_FAIL
+В заметках укажите, кто и что не видел, время UTC по G7.</t>
+        </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Сначала P1–P7 и G1–G8. Все изменения join/network.* выполняйте в файле MINECRAFT\config\skycraft.properties по G2–G5. Сначала L01 PASS. Поменять роли и получить новый LAN IPv4 по A1 на новом хосте.</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Успех при обеих ролях, отдельные архивы каждого ПК.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="59" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>L03</t>
+          <t>В «Прогоны → Движение обоим» YES только если оба видели движение друг друга. Запишите дрожание, откаты и задержку. Пинг берётся из отчёта R5, не оценивается на глаз.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="119" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Переподключение и уход хоста</t>
+          <t>Проверить блоки в обе стороны</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>DIRECT</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>5</v>
+          <t>Выберите свободный тестовый участок. E открывает инвентарь Minecraft; выберите обычные доски/камень и перенесите в панель быстрого доступа, Escape закрывает инвентарь. Клавиши 1–9 выбирают слот. ПКМ по поверхности ставит блок, удержание ЛКМ по поставленному блоку ломает его. Хост ставит 3 отдельных блока, клиент подтверждает каждый, затем хост ломает их и клиент подтверждает исчезновение. После этого хост наблюдает действия клиента.</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Подтвердите установку и удаление трёх блоков хоста, затем сами по тем же клавишам поставьте и сломайте три блока. После подтверждения обоими в чате:
+/skycraft debug mark BLOCK_BOTH_OK
+Если операция не дошла:
+/skycraft debug mark BLOCK_FAIL
+Запишите операцию, место и UTC.</t>
+        </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Сначала P1–P7 и G1–G8. Все изменения join/network.* выполняйте в файле MINECRAFT\config\skycraft.properties по G2–G5. Сначала L01 PASS; роли/адрес/режимы прежние.</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Понятный разрыв, без вечного автоповтора; повторный ручной вход работает.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="74" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>I01</t>
+          <t>«Блоки обоим» YES только после всех 12 операций: 3 установки + 3 удаления на каждой стороне. Не используйте TNT и разрушение поверхностей Skyrim. Если нет материалов или управление блоками не работает, запишите пропущенную проверку и PARTIAL; не считайте это доказательством сетевого сбоя.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="59" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Разные сети, прямой вход</t>
+          <t>Проверить стабильность</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>DIRECT</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>10</v>
+          <t>Играть число минут из сценария, не выключать хост. Двигаться/строить безопасные блоки, следить за клиентом. Записать фактическое начало/конец и число неожиданных разрывов.</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Играть те же минуты. При каждом разрыве записать время и сообщение. Пинг берётся из клиентского summary.json PingMeanMs/PingMaxMs; клиентские sample.ping_ms пишутся раз в 5 секунд.</t>
+        </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Сначала P1–P7 и G1–G8. Все изменения join/network.* выполняйте в файле MINECRAFT\config\skycraft.properties по G2–G5. Разные сети. Оба DIRECT без инструментов. Хост: A4–A7 либо смена ролей, если входящий адрес есть только у друга.</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Общий цикл проходит и сохраняются два отчёта.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="59" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>I02</t>
+          <t>Фактическая длительность не меньше требуемой. Любой разрыв записать, даже если повторный вход сработал. Краткий запуск — PARTIAL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="149" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>IPv6</t>
+          <t>Leave и повторный вход</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>DIRECT</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>5</v>
+          <t>Оставайтесь в мире. Поставьте один обычный блок в согласованном месте и оставьте его до повторного входа клиента. Клиент должен увидеть именно этот блок после возвращения.</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>В чате, по одной команде:
+/skycraft debug mark LEAVE_BEGIN
+/leave
+Дождитесь своего мира и работающего HUD, затем:
+/skycraft debug mark OWN_WORLD_OK
+/join ENDPOINT
+В последней команде используйте тот же реальный игровой адрес, что в шаге 5. После входа подтвердите оставленный блок:
+/skycraft debug mark REJOIN_OK</t>
+        </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Сначала P1–P7 и G1–G8. Все изменения join/network.* выполняйте в файле MINECRAFT\config\skycraft.properties по G2–G5. Оба имеют рабочий глобальный IPv6, DIRECT; выполнить A8–A9.</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Вход и 5 минут совместной игры проходят.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="74" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>N01</t>
+          <t>«Leave / rejoin» OK только если свой мир восстановился, затем загрузился мир хоста и сохранился оставленный блок. При неудаче FAIL с текстом ошибки и UTC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="89" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>zapret на клиенте</t>
+          <t>Остановить лог</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>DIRECT</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>5</v>
+          <t>В чате:
+/skycraft debug mark RUN_END
+/skycraft debug stop
+Подождите 2 секунды. Держите хост открытым, пока клиент тоже не завершил запись и сбор отчёта.</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>В чате:
+/skycraft debug mark RUN_END
+/skycraft debug stop
+Подождите 2 секунды. При аварийном закрытии игры сразу собирайте прежний ID без нового запуска.</t>
+        </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Сначала P1–P7 и G1–G8. Все изменения join/network.* выполняйте в файле MINECRAFT\config\skycraft.properties по G2–G5. Сначала I01/L01 PASS. Хост остаётся базовым. Клиент включает только zapret, network.mode=DIRECT.</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Сравнить с базовым прогоном; общий цикл, нет обрывов.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="74" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>N02</t>
+          <t>R2 объясняет завершение. В summary.json поле TraceStopped=true соответствует событию trace_closed; DroppedTraceEvents показывает потерянные события логгера. Если завершения нет, запишите незавершённый лог.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="89" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Cloudflare, только DNS на клиенте</t>
+          <t>Собрать ZIP</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>DIRECT</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>5</v>
+          <t>Запустите «Собрать отчёт.cmd» из распакованной папки P1. Режим 2. Заполните ВСЕ поля по R3–R4: путь G1, RUN_ID, Host, LAN/Internet, игровой адрес и отдельно порт, состояния своих программ и результат. Адрес тот же, которым пользовался клиент, включая внешний порт роутера.</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Та же программа → 2. Поля по R3–R4: путь G1, RUN_ID, Client, та же сеть и игровой адрес/порт. При прокси в поле IP по-прежнему игровой хост; прокси/режим записываются в Notes. Для IPv6 адрес без [] и без порта.</t>
+        </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Сначала P1–P7 и G1–G8. Все изменения join/network.* выполняйте в файле MINECRAFT\config\skycraft.properties по G2–G5. Сначала L01/I01 PASS. Только клиент: Cloudflare DNS-only, без перенаправления трафика; DIRECT по C1.</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Полный цикл по IP проходит. При наличии собственного DNS-имени повторный цикл по имени проходит; без имени DNS-часть BLOCKED.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="74" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>N03</t>
+          <t>Сборщик выводит полный путь ZIP. Оба берут свои файлы из reports в корне комплекта по R5. Должны быть два ZIP с одинаковым ID и разными ролями.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="89" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Cloudflare трафик + DNS (UDP)</t>
+          <t>Заполнить итог</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>DIRECT</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>10</v>
+          <t>Откройте рабочую XLSX, найдите строку RUN_ID в «Прогоны», заполните наблюдения и имя своего ZIP по R6. В «Условия прогонов» внесите адрес/источник и условия своего ПК. Согласуйте итог с клиентом.</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Из своего распакованного отчёта R5 возьмите summary.json: RemoteJoinElapsedMs, PingMeanMs, PingMaxMs. RemoteJoinElapsedMs может быть списком попыток: выберите нужную по events.csv world_join с result=remote и запишите какую. Внесите имя своего ZIP. null/отсутствующее значение оставьте пустым.</t>
+        </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Сначала P1–P7 и G1–G8. Все изменения join/network.* выполняйте в файле MINECRAFT\config\skycraft.properties по G2–G5. Сначала базовый PASS. Только клиент: Cloudflare трафик+DNS, выбранный DNS-протокол UDP; DIRECT.</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Установление соединения, блоки в обе стороны, 10 минут без разрывов.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="59" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>N04</t>
+          <t>PASS — выполнены все ожидания выбранного сценария; FAIL — ожидание нарушено; BLOCKED — нет условий; PARTIAL — часть шагов не проверена. Передайте два исходных ZIP и заполненную рабочую XLSX.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="104" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>X1</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>VPN-туннель на клиенте</t>
+          <t>Если вход не удался</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>DIRECT</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>10</v>
+          <t>Проверьте F2, запишите вывод LISTEN и оставался ли хост в своём мире. В чате:
+/skycraft debug mark JOIN_FAIL_HOST
+/skycraft debug stop
+Пауза 2 секунды, отчёт режима 2 по R3–R5 с прежним ID и Host.</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Запишите полный видимый текст ошибки и UTC G7. После возврата в свой мир:
+/skycraft debug mark JOIN_FAIL
+/skycraft debug stop
+Пауза 2 секунды, отчёт режима 2 с прежним ID и Client. Если игра упала, собирайте сразу, не запускайте снова.</t>
+        </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Сначала P1–P7 и G1–G8. Все изменения join/network.* выполняйте в файле MINECRAFT\config\skycraft.properties по G2–G5. Сначала базовый PASS. Только клиент: один VPN-туннель; DIRECT по C2.</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Игра следует маршрутам VPN, общий цикл проходит.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="74" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>N05</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Явный SOCKS5 VPN-клиента</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>SOCKS5</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Сначала P1–P7 и G1–G8. Все изменения join/network.* выполняйте в файле MINECRAFT\config\skycraft.properties по G2–G5. Сначала базовый PASS. Только клиент: включён SOCKS listener VPN-клиента; C3–C4.</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Удалённый DNS через прокси; TCP и игровой вход проходят.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="74" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>N06</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Явный HTTP CONNECT VPN-клиента</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>HTTP_CONNECT</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Сначала P1–P7 и G1–G8. Все изменения join/network.* выполняйте в файле MINECRAFT\config\skycraft.properties по G2–G5. Сначала базовый PASS. Только клиент: HTTP/mixed listener VPN-клиента; C3+C5.</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>В JSONL HTTP 200; вход в мир и изменения блоков проходят.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="74" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>N07</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>zapret + Cloudflare</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>DIRECT</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Сначала P1–P7 и G1–G8. Все изменения join/network.* выполняйте в файле MINECRAFT\config\skycraft.properties по G2–G5. Сначала N01/N03. Только клиент: zapret, затем Cloudflare traffic+DNS UDP; DIRECT.</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Сравнить с N01 и N03; 10 минут без разрывов.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="74" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>N08</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>zapret + Cloudflare + VPN-туннель</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>DIRECT</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Сначала P1–P7 и G1–G8. Все изменения join/network.* выполняйте в файле MINECRAFT\config\skycraft.properties по G2–G5. Сначала отдельные N01/N03/N04. Только клиент: zapret → Cloudflare traffic+DNS UDP → VPN tunnel; DIRECT.</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Вход и стабильность 15 минут; причины сбоев сравнить с одиночными режимами.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="74" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>N09</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Все инструменты + явный прокси</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>SOCKS5 / HTTP_CONNECT</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Сначала P1–P7 и G1–G8. Все изменения join/network.* выполняйте в файле MINECRAFT\config\skycraft.properties по G2–G5. Сначала N05/N06 и N07. Только клиент: zapret + Cloudflare traffic/DNS UDP + VPN в режиме системного прокси.</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Каждый транспорт оценивается отдельно; 15 минут игры на каждом доступном режиме.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="74" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>H01</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Инструменты на хосте</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>DIRECT</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Сначала P1–P7 и G1–G8. Все изменения join/network.* выполняйте в файле MINECRAFT\config\skycraft.properties по G2–G5. Сначала базовый PASS. Клиент остаётся базовым DIRECT. Хост включает zapret + Cloudflare traffic/DNS UDP.</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Проверить публикацию порта, вход клиента и стабильность каждого варианта.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="104" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>H02</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Инструменты на обоих ПК</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>DIRECT / явный прокси</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Сначала P1–P7 и G1–G8. Все изменения join/network.* выполняйте в файле MINECRAFT\config\skycraft.properties по G2–G5. Сначала H01 и нужный N08 либо N09 PASS. На обоих ПК zapret + Cloudflare трафик/DNS UDP + выбранный VPN. Для первой попытки оба VPN в режиме туннеля, клиент DIRECT C1. На хосте конфигурация SkyCraft C1; его VPN проверяется как изменение входящего маршрута.</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>15 минут, изменения в обе стороны, успешный /leave и повторный вход.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="44" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>E01</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Неправильный пароль прокси</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>SOCKS5 / HTTP_CONNECT</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Каждый транспорт отдельно; реальные секреты в Notes не писать.</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Отказ авторизации без зависания; восстановление пароля возвращает работоспособность.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="44" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>E02</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Отмена подключения</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>SOCKS5 / HTTP_CONNECT</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Нужна попытка, которая остаётся в ожидании достаточно долго.</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Поздний ответ не заменяет текущий мир; повторный вход работает; записать время отмены.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="104" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>E03</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>DNS-имя и IP одной цели</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>DIRECT / SOCKS5 / HTTP_CONNECT</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Сначала P1–P7 и G1–G8. Все изменения join/network.* выполняйте в файле MINECRAFT\config\skycraft.properties по G2–G5. Сначала рабочий I01. Требуется собственное DNS-имя, уже созданное владельцем домена и направленное на публичный IP хоста. Создание домена/DDNS в комплект не входит. Если имени нет — E03=BLOCKED, другие тесты по IP продолжайте.</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Выделить локальный DNS сбой в DIRECT и DNS/маршрут прокси в других режимах.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="104" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>E04</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>UDP недоступен</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>DIRECT / явный прокси</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Сначала P1–P7 и G1–G8. Все изменения join/network.* выполняйте в файле MINECRAFT\config\skycraft.properties по G2–G5. Дополнительный тест разработчика/подконтрольной сети. Готовая программа, которая блокирует и проверяет UDP, в комплект не входит. По умолчанию E04=BLOCKED: «нет подтверждённой среды без UDP». Не меняйте общий firewall или DNS Windows ради этого теста.</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Проверить Minecraft TCP при этих условиях, отметить возможный отказ самого VPN/DNS.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="89" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>E05</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Переключение сети во время игры</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>DIRECT / явный прокси</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Сначала P1–P7 и G1–G8. Все изменения join/network.* выполняйте в файле MINECRAFT\config\skycraft.properties по G2–G5. Сначала N04 либо N05/N06 PASS. Клиент заранее выбирает второй рабочий VPN-сервер/профиль в своей программе, записывает исходный и новый профиль без ключей. Хост и игровой адрес сохраняются.</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Смена маршрута может оборвать TCP; требуется понятный разрыв и работоспособность ручного входа после стабилизации.</t>
+          <t>После отказа пропустите шаги 6–9. Для новой попытки новый номер ID. Сохраните оба отчёта даже при неуспехе.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId25"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -18354,7 +18853,7 @@
     <firstFooter/>
   </headerFooter>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId26"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>